--- a/data/Results_Discussion_Notes.xlsx
+++ b/data/Results_Discussion_Notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobregeo\Documents\GitHub\vilearn_ml\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2A13A9-1594-4604-B6B5-5CA6583274A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3A72A5-9A50-4635-A84C-BA4AB8D5F2D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15915" yWindow="0" windowWidth="12990" windowHeight="15585" tabRatio="279" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="519" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,6 +36,12 @@
     <definedName name="_xlchart.v1.9" hidden="1">MeanBlinkAsyncMS!$C$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
+    <pivotCache cacheId="3" r:id="rId10"/>
+    <pivotCache cacheId="7" r:id="rId11"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -56,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="278">
   <si>
     <t>Group</t>
   </si>
@@ -788,12 +794,141 @@
   <si>
     <t>similar setting in non-vr</t>
   </si>
+  <si>
+    <t>group_name_short</t>
+  </si>
+  <si>
+    <t>dyad_01</t>
+  </si>
+  <si>
+    <t>dyad_02</t>
+  </si>
+  <si>
+    <t>dyad_03</t>
+  </si>
+  <si>
+    <t>dyad_04</t>
+  </si>
+  <si>
+    <t>dyad_05</t>
+  </si>
+  <si>
+    <t>dyad_06</t>
+  </si>
+  <si>
+    <t>dyad_07</t>
+  </si>
+  <si>
+    <t>dyad_08</t>
+  </si>
+  <si>
+    <t>dyad_09</t>
+  </si>
+  <si>
+    <t>dyad_10</t>
+  </si>
+  <si>
+    <t>dyad_11</t>
+  </si>
+  <si>
+    <t>triad_01</t>
+  </si>
+  <si>
+    <t>triad_02</t>
+  </si>
+  <si>
+    <t>triad_03</t>
+  </si>
+  <si>
+    <t>triad_04</t>
+  </si>
+  <si>
+    <t>triad_05</t>
+  </si>
+  <si>
+    <t>triad_06</t>
+  </si>
+  <si>
+    <t>triad_07</t>
+  </si>
+  <si>
+    <t>triad_08</t>
+  </si>
+  <si>
+    <t>triad_09</t>
+  </si>
+  <si>
+    <t>triad_10</t>
+  </si>
+  <si>
+    <t>triad_11</t>
+  </si>
+  <si>
+    <t>triad_12</t>
+  </si>
+  <si>
+    <t>triad_13</t>
+  </si>
+  <si>
+    <t>triad_14</t>
+  </si>
+  <si>
+    <t>Gender analysis</t>
+  </si>
+  <si>
+    <t>P1_gender</t>
+  </si>
+  <si>
+    <t>P2_gender</t>
+  </si>
+  <si>
+    <t>P3_gender</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>mean_blink_duration_ms</t>
+  </si>
+  <si>
+    <t>Average of mean_blink_duration_ms</t>
+  </si>
+  <si>
+    <t>short_group_name</t>
+  </si>
+  <si>
+    <t>BRM</t>
+  </si>
+  <si>
+    <t>Average of BRM</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -849,8 +984,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -869,8 +1019,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor theme="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -898,11 +1054,66 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -941,11 +1152,45 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="46">
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -969,6 +1214,351 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9.8000000000000007"/>
+        <color auto="1"/>
+        <name val="JetBrains Mono"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9.8000000000000007"/>
+        <color auto="1"/>
+        <name val="JetBrains Mono"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9.8000000000000007"/>
+        <color auto="1"/>
+        <name val="JetBrains Mono"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9.8000000000000007"/>
+        <color auto="1"/>
+        <name val="JetBrains Mono"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9.8000000000000007"/>
+        <color auto="1"/>
+        <name val="JetBrains Mono"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9.8000000000000007"/>
+        <color auto="1"/>
+        <name val="JetBrains Mono"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9.8000000000000007"/>
+        <color auto="1"/>
+        <name val="JetBrains Mono"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9.8000000000000007"/>
+        <color auto="1"/>
+        <name val="JetBrains Mono"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9.8000000000000007"/>
+        <color auto="1"/>
+        <name val="JetBrains Mono"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1240,6 +1830,201 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="1"/>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5614,7 +6399,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -15397,8 +16182,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="13674725" y="2978150"/>
-              <a:ext cx="4124325" cy="2743200"/>
+              <a:off x="15313025" y="3079750"/>
+              <a:ext cx="5073650" cy="2841625"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -15778,8 +16563,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12794504" y="11462871"/>
-              <a:ext cx="4552202" cy="2699123"/>
+              <a:off x="13775579" y="11862921"/>
+              <a:ext cx="5241177" cy="2788023"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -16102,8 +16887,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="7856538" y="5314950"/>
-              <a:ext cx="3322637" cy="2270126"/>
+              <a:off x="7748588" y="5499100"/>
+              <a:ext cx="3211512" cy="2355851"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -16185,8 +16970,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="164773" y="2970268"/>
-              <a:ext cx="4057758" cy="3266090"/>
+              <a:off x="164773" y="3071868"/>
+              <a:ext cx="4057758" cy="3383565"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -16348,6 +17133,958 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Georgiana Cristina Dobre" refreshedDate="45909.628909606479" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="22" xr:uid="{77026A98-5BF3-494A-8C44-DC2A6941EB79}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table15"/>
+  </cacheSource>
+  <cacheFields count="3">
+    <cacheField name="group_name_short" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="gender" numFmtId="0">
+      <sharedItems count="2">
+        <s v="F"/>
+        <s v="M"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="mean_blink_duration_ms" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="155.07327599999999" maxValue="259.644836"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Georgiana Cristina Dobre" refreshedDate="45909.629982986109" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="42" xr:uid="{4A7EBD6F-E6BC-4DB1-9085-399A4F73DACA}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table16"/>
+  </cacheSource>
+  <cacheFields count="3">
+    <cacheField name="group_name_short" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="gender" numFmtId="0">
+      <sharedItems count="2">
+        <s v="F"/>
+        <s v="M"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="mean_blink_duration_ms" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="125.67857100000001" maxValue="253.12820500000001"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Georgiana Cristina Dobre" refreshedDate="45909.637240856478" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="42" xr:uid="{AC9A1C47-8C71-497E-AA51-4BDB71FDFD9D}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table20"/>
+  </cacheSource>
+  <cacheFields count="3">
+    <cacheField name="group_name_short" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="gender" numFmtId="0">
+      <sharedItems count="2">
+        <s v="F"/>
+        <s v="M"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="BRM" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.2134100000000001" maxValue="58.124909000000002"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Georgiana Cristina Dobre" refreshedDate="45910.560668518519" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="22" xr:uid="{26F17996-E6F6-4253-BF34-9248E19535C9}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table19"/>
+  </cacheSource>
+  <cacheFields count="3">
+    <cacheField name="short_group_name" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="gender" numFmtId="0">
+      <sharedItems count="2">
+        <s v="F"/>
+        <s v="M"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="BRM" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.4711409999999998" maxValue="60.294035000000001"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="22">
+  <r>
+    <s v="dyad_01"/>
+    <x v="0"/>
+    <n v="155.283019"/>
+  </r>
+  <r>
+    <s v="dyad_02"/>
+    <x v="1"/>
+    <n v="218.36752100000001"/>
+  </r>
+  <r>
+    <s v="dyad_03"/>
+    <x v="0"/>
+    <n v="204.75380699999999"/>
+  </r>
+  <r>
+    <s v="dyad_04"/>
+    <x v="0"/>
+    <n v="155.45097999999999"/>
+  </r>
+  <r>
+    <s v="dyad_05"/>
+    <x v="1"/>
+    <n v="241.208955"/>
+  </r>
+  <r>
+    <s v="dyad_06"/>
+    <x v="1"/>
+    <n v="210.85906"/>
+  </r>
+  <r>
+    <s v="dyad_07"/>
+    <x v="1"/>
+    <n v="193.80620200000001"/>
+  </r>
+  <r>
+    <s v="dyad_08"/>
+    <x v="1"/>
+    <n v="158.79097400000001"/>
+  </r>
+  <r>
+    <s v="dyad_09"/>
+    <x v="0"/>
+    <n v="159.34567899999999"/>
+  </r>
+  <r>
+    <s v="dyad_10"/>
+    <x v="1"/>
+    <n v="233.86496399999999"/>
+  </r>
+  <r>
+    <s v="dyad_11"/>
+    <x v="1"/>
+    <n v="162.87719300000001"/>
+  </r>
+  <r>
+    <s v="dyad_01"/>
+    <x v="0"/>
+    <n v="175.88665"/>
+  </r>
+  <r>
+    <s v="dyad_02"/>
+    <x v="0"/>
+    <n v="259.644836"/>
+  </r>
+  <r>
+    <s v="dyad_03"/>
+    <x v="0"/>
+    <n v="162.682692"/>
+  </r>
+  <r>
+    <s v="dyad_04"/>
+    <x v="0"/>
+    <n v="176.07033000000001"/>
+  </r>
+  <r>
+    <s v="dyad_05"/>
+    <x v="1"/>
+    <n v="190.61299399999999"/>
+  </r>
+  <r>
+    <s v="dyad_06"/>
+    <x v="0"/>
+    <n v="185.06127499999999"/>
+  </r>
+  <r>
+    <s v="dyad_07"/>
+    <x v="1"/>
+    <n v="155.07327599999999"/>
+  </r>
+  <r>
+    <s v="dyad_08"/>
+    <x v="0"/>
+    <n v="193.030303"/>
+  </r>
+  <r>
+    <s v="dyad_09"/>
+    <x v="0"/>
+    <n v="186.157534"/>
+  </r>
+  <r>
+    <s v="dyad_10"/>
+    <x v="1"/>
+    <n v="190.47191000000001"/>
+  </r>
+  <r>
+    <s v="dyad_11"/>
+    <x v="1"/>
+    <n v="201.66666699999999"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="42">
+  <r>
+    <s v="triad_01"/>
+    <x v="0"/>
+    <n v="192.61988299999999"/>
+  </r>
+  <r>
+    <s v="triad_03"/>
+    <x v="0"/>
+    <n v="140.052885"/>
+  </r>
+  <r>
+    <s v="triad_04"/>
+    <x v="0"/>
+    <n v="125.67857100000001"/>
+  </r>
+  <r>
+    <s v="triad_05"/>
+    <x v="0"/>
+    <n v="197.77333300000001"/>
+  </r>
+  <r>
+    <s v="triad_06"/>
+    <x v="0"/>
+    <n v="148.419355"/>
+  </r>
+  <r>
+    <s v="triad_07"/>
+    <x v="0"/>
+    <n v="133.942857"/>
+  </r>
+  <r>
+    <s v="triad_08"/>
+    <x v="0"/>
+    <n v="206.78022000000001"/>
+  </r>
+  <r>
+    <s v="triad_09"/>
+    <x v="0"/>
+    <n v="170.885965"/>
+  </r>
+  <r>
+    <s v="triad_02"/>
+    <x v="0"/>
+    <n v="190.14367799999999"/>
+  </r>
+  <r>
+    <s v="triad_11"/>
+    <x v="1"/>
+    <n v="149.02941200000001"/>
+  </r>
+  <r>
+    <s v="triad_10"/>
+    <x v="1"/>
+    <n v="179.045455"/>
+  </r>
+  <r>
+    <s v="triad_14"/>
+    <x v="0"/>
+    <n v="155.252137"/>
+  </r>
+  <r>
+    <s v="triad_12"/>
+    <x v="1"/>
+    <n v="190.340136"/>
+  </r>
+  <r>
+    <s v="triad_13"/>
+    <x v="0"/>
+    <n v="150.79701499999999"/>
+  </r>
+  <r>
+    <s v="triad_01"/>
+    <x v="1"/>
+    <n v="153.51952"/>
+  </r>
+  <r>
+    <s v="triad_03"/>
+    <x v="0"/>
+    <n v="175.77197799999999"/>
+  </r>
+  <r>
+    <s v="triad_04"/>
+    <x v="1"/>
+    <n v="171.88356200000001"/>
+  </r>
+  <r>
+    <s v="triad_05"/>
+    <x v="0"/>
+    <n v="165.45217400000001"/>
+  </r>
+  <r>
+    <s v="triad_06"/>
+    <x v="0"/>
+    <n v="213.963964"/>
+  </r>
+  <r>
+    <s v="triad_07"/>
+    <x v="0"/>
+    <n v="253.12820500000001"/>
+  </r>
+  <r>
+    <s v="triad_08"/>
+    <x v="1"/>
+    <n v="174.05384599999999"/>
+  </r>
+  <r>
+    <s v="triad_09"/>
+    <x v="0"/>
+    <n v="240.30364399999999"/>
+  </r>
+  <r>
+    <s v="triad_02"/>
+    <x v="1"/>
+    <n v="176.79674800000001"/>
+  </r>
+  <r>
+    <s v="triad_11"/>
+    <x v="0"/>
+    <n v="165.265152"/>
+  </r>
+  <r>
+    <s v="triad_10"/>
+    <x v="1"/>
+    <n v="181.13793100000001"/>
+  </r>
+  <r>
+    <s v="triad_14"/>
+    <x v="0"/>
+    <n v="194.52795"/>
+  </r>
+  <r>
+    <s v="triad_12"/>
+    <x v="1"/>
+    <n v="168.39919399999999"/>
+  </r>
+  <r>
+    <s v="triad_13"/>
+    <x v="0"/>
+    <n v="156.904977"/>
+  </r>
+  <r>
+    <s v="triad_01"/>
+    <x v="0"/>
+    <n v="166.052301"/>
+  </r>
+  <r>
+    <s v="triad_03"/>
+    <x v="0"/>
+    <n v="235.84090900000001"/>
+  </r>
+  <r>
+    <s v="triad_04"/>
+    <x v="0"/>
+    <n v="172.36824300000001"/>
+  </r>
+  <r>
+    <s v="triad_05"/>
+    <x v="0"/>
+    <n v="156.27201099999999"/>
+  </r>
+  <r>
+    <s v="triad_06"/>
+    <x v="0"/>
+    <n v="182.36454800000001"/>
+  </r>
+  <r>
+    <s v="triad_07"/>
+    <x v="0"/>
+    <n v="166.39393899999999"/>
+  </r>
+  <r>
+    <s v="triad_08"/>
+    <x v="0"/>
+    <n v="162.85869600000001"/>
+  </r>
+  <r>
+    <s v="triad_09"/>
+    <x v="0"/>
+    <n v="178.34482800000001"/>
+  </r>
+  <r>
+    <s v="triad_02"/>
+    <x v="0"/>
+    <n v="193.95132699999999"/>
+  </r>
+  <r>
+    <s v="triad_11"/>
+    <x v="0"/>
+    <n v="226.71977999999999"/>
+  </r>
+  <r>
+    <s v="triad_10"/>
+    <x v="0"/>
+    <n v="153.97183100000001"/>
+  </r>
+  <r>
+    <s v="triad_14"/>
+    <x v="1"/>
+    <n v="173.75877199999999"/>
+  </r>
+  <r>
+    <s v="triad_12"/>
+    <x v="1"/>
+    <n v="227.647887"/>
+  </r>
+  <r>
+    <s v="triad_13"/>
+    <x v="1"/>
+    <n v="177.014218"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="42">
+  <r>
+    <s v="triad_01"/>
+    <x v="0"/>
+    <n v="13.27946"/>
+  </r>
+  <r>
+    <s v="triad_03"/>
+    <x v="0"/>
+    <n v="18.098331000000002"/>
+  </r>
+  <r>
+    <s v="triad_04"/>
+    <x v="0"/>
+    <n v="2.2134100000000001"/>
+  </r>
+  <r>
+    <s v="triad_05"/>
+    <x v="0"/>
+    <n v="24.187462"/>
+  </r>
+  <r>
+    <s v="triad_06"/>
+    <x v="0"/>
+    <n v="13.098208"/>
+  </r>
+  <r>
+    <s v="triad_07"/>
+    <x v="0"/>
+    <n v="9.9307610000000004"/>
+  </r>
+  <r>
+    <s v="triad_08"/>
+    <x v="0"/>
+    <n v="18.789473999999998"/>
+  </r>
+  <r>
+    <s v="triad_09"/>
+    <x v="0"/>
+    <n v="13.606121"/>
+  </r>
+  <r>
+    <s v="triad_02"/>
+    <x v="0"/>
+    <n v="31.080375"/>
+  </r>
+  <r>
+    <s v="triad_11"/>
+    <x v="1"/>
+    <n v="32.160544999999999"/>
+  </r>
+  <r>
+    <s v="triad_10"/>
+    <x v="1"/>
+    <n v="15.797788000000001"/>
+  </r>
+  <r>
+    <s v="triad_14"/>
+    <x v="0"/>
+    <n v="21.965651999999999"/>
+  </r>
+  <r>
+    <s v="triad_12"/>
+    <x v="1"/>
+    <n v="18.728362000000001"/>
+  </r>
+  <r>
+    <s v="triad_13"/>
+    <x v="0"/>
+    <n v="28.657671000000001"/>
+  </r>
+  <r>
+    <s v="triad_01"/>
+    <x v="1"/>
+    <n v="26.720863999999999"/>
+  </r>
+  <r>
+    <s v="triad_03"/>
+    <x v="0"/>
+    <n v="29.803229999999999"/>
+  </r>
+  <r>
+    <s v="triad_04"/>
+    <x v="1"/>
+    <n v="11.462300000000001"/>
+  </r>
+  <r>
+    <s v="triad_05"/>
+    <x v="0"/>
+    <n v="7.7812380000000001"/>
+  </r>
+  <r>
+    <s v="triad_06"/>
+    <x v="0"/>
+    <n v="8.8605520000000002"/>
+  </r>
+  <r>
+    <s v="triad_07"/>
+    <x v="0"/>
+    <n v="10.206614999999999"/>
+  </r>
+  <r>
+    <s v="triad_08"/>
+    <x v="1"/>
+    <n v="14.210526"/>
+  </r>
+  <r>
+    <s v="triad_09"/>
+    <x v="0"/>
+    <n v="26.940118999999999"/>
+  </r>
+  <r>
+    <s v="triad_02"/>
+    <x v="1"/>
+    <n v="10.094481"/>
+  </r>
+  <r>
+    <s v="triad_11"/>
+    <x v="0"/>
+    <n v="19.296327000000002"/>
+  </r>
+  <r>
+    <s v="triad_10"/>
+    <x v="1"/>
+    <n v="20.227074999999999"/>
+  </r>
+  <r>
+    <s v="triad_14"/>
+    <x v="0"/>
+    <n v="14.677982999999999"/>
+  </r>
+  <r>
+    <s v="triad_12"/>
+    <x v="1"/>
+    <n v="28.883882"/>
+  </r>
+  <r>
+    <s v="triad_13"/>
+    <x v="0"/>
+    <n v="20.567240000000002"/>
+  </r>
+  <r>
+    <s v="triad_01"/>
+    <x v="0"/>
+    <n v="36.113652999999999"/>
+  </r>
+  <r>
+    <s v="triad_03"/>
+    <x v="0"/>
+    <n v="14.655714"/>
+  </r>
+  <r>
+    <s v="triad_04"/>
+    <x v="0"/>
+    <n v="22.608398000000001"/>
+  </r>
+  <r>
+    <s v="triad_05"/>
+    <x v="0"/>
+    <n v="58.124909000000002"/>
+  </r>
+  <r>
+    <s v="triad_06"/>
+    <x v="0"/>
+    <n v="23.981276999999999"/>
+  </r>
+  <r>
+    <s v="triad_07"/>
+    <x v="0"/>
+    <n v="6.4825799999999996"/>
+  </r>
+  <r>
+    <s v="triad_08"/>
+    <x v="0"/>
+    <n v="7.4210529999999997"/>
+  </r>
+  <r>
+    <s v="triad_09"/>
+    <x v="0"/>
+    <n v="34.287424999999999"/>
+  </r>
+  <r>
+    <s v="triad_02"/>
+    <x v="0"/>
+    <n v="17.930986000000001"/>
+  </r>
+  <r>
+    <s v="triad_11"/>
+    <x v="0"/>
+    <n v="21.611886999999999"/>
+  </r>
+  <r>
+    <s v="triad_10"/>
+    <x v="0"/>
+    <n v="18.307717"/>
+  </r>
+  <r>
+    <s v="triad_14"/>
+    <x v="1"/>
+    <n v="21.452435999999999"/>
+  </r>
+  <r>
+    <s v="triad_12"/>
+    <x v="1"/>
+    <n v="17.541353000000001"/>
+  </r>
+  <r>
+    <s v="triad_13"/>
+    <x v="1"/>
+    <n v="19.592489"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="22">
+  <r>
+    <s v="dyad_01"/>
+    <x v="0"/>
+    <n v="2.4711409999999998"/>
+  </r>
+  <r>
+    <s v="dyad_03"/>
+    <x v="0"/>
+    <n v="32.033904"/>
+  </r>
+  <r>
+    <s v="dyad_04"/>
+    <x v="0"/>
+    <n v="38.272494999999999"/>
+  </r>
+  <r>
+    <s v="dyad_09"/>
+    <x v="0"/>
+    <n v="5.3683930000000002"/>
+  </r>
+  <r>
+    <s v="dyad_01"/>
+    <x v="0"/>
+    <n v="30.938687999999999"/>
+  </r>
+  <r>
+    <s v="dyad_02"/>
+    <x v="0"/>
+    <n v="31.456980000000001"/>
+  </r>
+  <r>
+    <s v="dyad_03"/>
+    <x v="0"/>
+    <n v="34.357607000000002"/>
+  </r>
+  <r>
+    <s v="dyad_04"/>
+    <x v="0"/>
+    <n v="39.090671999999998"/>
+  </r>
+  <r>
+    <s v="dyad_06"/>
+    <x v="0"/>
+    <n v="38.751725"/>
+  </r>
+  <r>
+    <s v="dyad_08"/>
+    <x v="0"/>
+    <n v="25.324967000000001"/>
+  </r>
+  <r>
+    <s v="dyad_09"/>
+    <x v="0"/>
+    <n v="24.631449"/>
+  </r>
+  <r>
+    <s v="dyad_02"/>
+    <x v="1"/>
+    <n v="32.792991000000001"/>
+  </r>
+  <r>
+    <s v="dyad_05"/>
+    <x v="1"/>
+    <n v="17.652170000000002"/>
+  </r>
+  <r>
+    <s v="dyad_06"/>
+    <x v="1"/>
+    <n v="13.541086"/>
+  </r>
+  <r>
+    <s v="dyad_07"/>
+    <x v="1"/>
+    <n v="22.615593000000001"/>
+  </r>
+  <r>
+    <s v="dyad_08"/>
+    <x v="1"/>
+    <n v="60.294035000000001"/>
+  </r>
+  <r>
+    <s v="dyad_10"/>
+    <x v="1"/>
+    <n v="27.407136999999999"/>
+  </r>
+  <r>
+    <s v="dyad_11"/>
+    <x v="1"/>
+    <n v="18.118190999999999"/>
+  </r>
+  <r>
+    <s v="dyad_05"/>
+    <x v="1"/>
+    <n v="30.456852999999999"/>
+  </r>
+  <r>
+    <s v="dyad_07"/>
+    <x v="1"/>
+    <n v="41.354227999999999"/>
+  </r>
+  <r>
+    <s v="dyad_10"/>
+    <x v="1"/>
+    <n v="20.296095999999999"/>
+  </r>
+  <r>
+    <s v="dyad_11"/>
+    <x v="1"/>
+    <n v="35.347144999999998"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DCF267E0-450F-4AA8-AE38-530E9372F322}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E68:F71" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of mean_blink_duration_ms" fld="2" subtotal="average" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B0FE5B86-9557-460C-87A8-743CCEBCEE57}" name="PivotTable15" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="P69:Q72" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of mean_blink_duration_ms" fld="2" subtotal="average" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B12DF9C4-357E-4B31-A6A9-48544674DC20}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="F150:G153" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of BRM" fld="2" subtotal="average" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04B2A65A-0C8B-4918-8B54-3F35DB31E132}" name="PivotTable17" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="O154:P157" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of BRM" fld="2" subtotal="average" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{F6ED4B9B-8B77-46CF-A6E2-C270AF52D3C7}" name="Table7" displayName="Table7" ref="B1:F12" totalsRowShown="0">
   <autoFilter ref="B1:F12" xr:uid="{F6ED4B9B-8B77-46CF-A6E2-C270AF52D3C7}"/>
@@ -16363,6 +18100,129 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{36BB00D6-4E8F-43D5-B2C8-30587CF65EDD}" name="Table18" displayName="Table18" ref="K135:R149" totalsRowShown="0" dataDxfId="23">
+  <autoFilter ref="K135:R149" xr:uid="{36BB00D6-4E8F-43D5-B2C8-30587CF65EDD}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{B561AF8A-A679-4EE7-9AD8-A252E27AD6DE}" name="group_name_short"/>
+    <tableColumn id="2" xr3:uid="{3964AECF-0546-4935-88E8-78044B9787C9}" name="Group" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{23607895-900C-4358-A84D-9A0B49943197}" name="P1_gender" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{AD0DA697-B1F9-4314-AF88-ECCE06589085}" name="P1" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{8532E42C-2EBB-4FA2-ABF1-E0C966F8EB80}" name="P2_gender" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{9EEC63F9-8552-48A3-A4FC-CBD1F24A0800}" name="P2" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{05C50DDE-E161-47EB-9CEB-160AC592895B}" name="P3_gender" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{2FE32403-7E04-46D4-8E2C-D057CA9AA5E6}" name="P3" dataDxfId="16"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{59D2BFEB-9EBC-4409-8123-28BF7ED9F05D}" name="Table19" displayName="Table19" ref="B150:D172" totalsRowShown="0" tableBorderDxfId="15">
+  <autoFilter ref="B150:D172" xr:uid="{59D2BFEB-9EBC-4409-8123-28BF7ED9F05D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B151:D172">
+    <sortCondition ref="C150:C172"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{2C10C56B-5C5A-4405-AB12-9FC7EF3667C6}" name="short_group_name" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{C201F025-F75E-4FB3-9148-28A1DB5E99AB}" name="gender" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{22E9C4A0-683B-4125-94F6-E3257F38D7D0}" name="BRM" dataDxfId="12"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{CC86123F-88D7-41B5-B44A-4D30383D92E0}" name="Table20" displayName="Table20" ref="K154:M196" totalsRowShown="0" tableBorderDxfId="11">
+  <autoFilter ref="K154:M196" xr:uid="{CC86123F-88D7-41B5-B44A-4D30383D92E0}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K155:M196">
+    <sortCondition ref="L154:L196"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{A19875F5-FDAB-4774-A356-9695FBF140A6}" name="group_name_short" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{92E84300-25AF-43BF-8FDC-239C36342AAE}" name="gender" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{F9D3D3DA-802C-4377-A3ED-C54D3FF4E4FF}" name="BRM" dataDxfId="8"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2DDE5A9D-30CA-46ED-97F0-1C4FEC122E36}" name="Table3" displayName="Table3" ref="I2:M13" totalsRowShown="0">
+  <autoFilter ref="I2:M13" xr:uid="{2DDE5A9D-30CA-46ED-97F0-1C4FEC122E36}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{3F2D9A49-CB8D-42DB-9308-C8C69690D536}" name="group_name"/>
+    <tableColumn id="2" xr3:uid="{52DE6ABD-824B-4973-B79D-365B55975AD4}" name="group_size"/>
+    <tableColumn id="3" xr3:uid="{F4EE57F7-134D-4B1D-A183-5A5DB8EC2A51}" name="count_blinks_participant_reference"/>
+    <tableColumn id="4" xr3:uid="{13D1FF19-31EE-4C8B-8D48-6D9C1440961D}" name="count_sync_blinks"/>
+    <tableColumn id="5" xr3:uid="{EBCD6D38-DA7A-4B32-A832-56FD5FE27505}" name="percent_sync_blinks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9C85DFC2-8853-442F-82F5-FC50BCDA248D}" name="Table4" displayName="Table4" ref="P2:T16" totalsRowShown="0">
+  <autoFilter ref="P2:T16" xr:uid="{9C85DFC2-8853-442F-82F5-FC50BCDA248D}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{4EBA4596-D512-4014-8443-5406E0A17D40}" name="group_name"/>
+    <tableColumn id="2" xr3:uid="{6BE7A398-823C-4857-870A-1AF477ADDFF4}" name="group_size"/>
+    <tableColumn id="3" xr3:uid="{155A14E7-67CE-47D1-ABCB-DA40DBA3CD30}" name="count_blinks_participant_reference"/>
+    <tableColumn id="4" xr3:uid="{7A67B0EE-5289-48DB-8223-9B55BE9C9BCB}" name="count_sync_blinks"/>
+    <tableColumn id="5" xr3:uid="{7D7D6422-F269-4D6B-ACA7-3BF34AF789DD}" name="percent_sync_blinks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8C25D1AD-2854-40AA-8354-72C5021373BA}" name="Table5" displayName="Table5" ref="G1:J12" totalsRowShown="0">
+  <autoFilter ref="G1:J12" xr:uid="{8C25D1AD-2854-40AA-8354-72C5021373BA}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{6D40A87A-BB4C-4E8C-B2B2-45A314637EAB}" name="group_name"/>
+    <tableColumn id="2" xr3:uid="{44B8A537-3D3D-4A32-A4E9-A479A2FBAEB8}" name="group_size"/>
+    <tableColumn id="3" xr3:uid="{E56604FE-4744-4494-96E9-2E228A162AAB}" name="count_sync_blinks"/>
+    <tableColumn id="4" xr3:uid="{23F049FC-98FA-4630-A819-6E88CF2BB14F}" name="avg_blinks_async_ms"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{F064CA2C-1F70-44B8-BBA9-1279DE17B6FA}" name="Table6" displayName="Table6" ref="N1:Q15" totalsRowShown="0">
+  <autoFilter ref="N1:Q15" xr:uid="{F064CA2C-1F70-44B8-BBA9-1279DE17B6FA}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{5590ACE3-601B-4874-B2FD-40E7CE33D13C}" name="group_name"/>
+    <tableColumn id="2" xr3:uid="{DBD04632-1B48-46B6-8176-FBFC5676F488}" name="group_size"/>
+    <tableColumn id="3" xr3:uid="{E2EF6420-C922-43B5-A67E-B09B3D8CAC04}" name="count_sync_blinks"/>
+    <tableColumn id="4" xr3:uid="{C1FE3794-32D2-4348-A14B-DA8E4EC94C43}" name="avg_blinks_async_ms"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{87D36C7E-4AD2-425A-BAE4-7F65D68961B3}" name="Table9" displayName="Table9" ref="B2:N13" totalsRowShown="0">
+  <autoFilter ref="B2:N13" xr:uid="{87D36C7E-4AD2-425A-BAE4-7F65D68961B3}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{9BC1567B-64A2-4977-B462-E55CD1930503}" name="group index"/>
+    <tableColumn id="2" xr3:uid="{22340563-374A-41E8-9D56-C75D1890ED3F}" name="-1500"/>
+    <tableColumn id="3" xr3:uid="{1FF8687A-8105-4FD8-BEA2-D5AB4CC51840}" name="-1250"/>
+    <tableColumn id="4" xr3:uid="{351898DC-892A-48D0-BC44-899BCD29B003}" name="-1000"/>
+    <tableColumn id="5" xr3:uid="{10ABA271-061E-4E25-93AA-23D298B61FA2}" name="-750"/>
+    <tableColumn id="6" xr3:uid="{A8A1DE2D-6ACD-4369-A468-5E4751A4E065}" name="-500"/>
+    <tableColumn id="7" xr3:uid="{1D598D59-4409-4DA8-B18C-34B02FFF856B}" name="-250"/>
+    <tableColumn id="8" xr3:uid="{D541AF2B-E7C2-471F-AFF0-AD9BCA3B328A}" name="0"/>
+    <tableColumn id="9" xr3:uid="{F633A798-9031-42A6-9031-A0988867361C}" name="250"/>
+    <tableColumn id="10" xr3:uid="{321CCB05-D4C5-4E13-B6C6-D0D29029B8CA}" name="500"/>
+    <tableColumn id="11" xr3:uid="{64A44B7D-08D9-4B98-9EF3-E5A3A28326A0}" name="750"/>
+    <tableColumn id="12" xr3:uid="{485F7809-F3B6-4A67-8541-C8D4A372FC10}" name="1000"/>
+    <tableColumn id="13" xr3:uid="{8F82B826-F05C-4ED9-AB02-311044D91A11}" name="1250"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{2FE4F5CA-2757-4BB8-B7D4-6FAD0F9D3313}" name="Table10" displayName="Table10" ref="S2:AE16" totalsRowShown="0">
   <autoFilter ref="S2:AE16" xr:uid="{2FE4F5CA-2757-4BB8-B7D4-6FAD0F9D3313}"/>
   <tableColumns count="13">
@@ -16384,16 +18244,16 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{AE3128D6-0977-4CDB-9564-6576F6CC0F00}" name="Table12" displayName="Table12" ref="B3:G9" totalsRowShown="0" headerRowDxfId="7" dataDxfId="1">
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{AE3128D6-0977-4CDB-9564-6576F6CC0F00}" name="Table12" displayName="Table12" ref="B3:G9" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="B3:G9" xr:uid="{AE3128D6-0977-4CDB-9564-6576F6CC0F00}"/>
   <tableColumns count="6">
-    <tableColumn id="7" xr3:uid="{9ADAD039-B1E9-4CE9-A97A-F011BE916F7E}" name="Studies" dataDxfId="6"/>
-    <tableColumn id="1" xr3:uid="{82438DF6-BD05-4592-A8DD-7774EC290540}" name="Blink Duration" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{73A7EFA3-1D5A-46CB-8FDD-FC9B98AFF790}" name="Blink Rate" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{870B7377-D9C2-43BC-BF44-555251957991}" name="% synced blinks" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{2CBBC7E0-C34D-4EDC-BAF8-1044465DAD77}" name="Mean Asynced blinks time" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{0FE01176-586C-4503-854F-0ADC1D5FE9ED}" name="Asynced blinks temporal" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{9ADAD039-B1E9-4CE9-A97A-F011BE916F7E}" name="Studies" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{82438DF6-BD05-4592-A8DD-7774EC290540}" name="Blink Duration" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{73A7EFA3-1D5A-46CB-8FDD-FC9B98AFF790}" name="Blink Rate" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{870B7377-D9C2-43BC-BF44-555251957991}" name="% synced blinks" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{2CBBC7E0-C34D-4EDC-BAF8-1044465DAD77}" name="Mean Asynced blinks time" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{0FE01176-586C-4503-854F-0ADC1D5FE9ED}" name="Asynced blinks temporal" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16415,13 +18275,79 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AD080257-BFA1-460B-B07A-36A64761A16A}" name="Table1" displayName="Table1" ref="C1:F12" totalsRowShown="0" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{74760145-4C16-4033-A82E-87B229559550}" name="Table13" displayName="Table13" ref="A53:H64" totalsRowShown="0">
+  <autoFilter ref="A53:H64" xr:uid="{74760145-4C16-4033-A82E-87B229559550}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{A1A067A2-BAA2-40FA-9BF4-7FEFA08FB528}" name="group_name_short"/>
+    <tableColumn id="2" xr3:uid="{87ECF523-110D-4154-B3A5-8887AF7A0F46}" name="group_name"/>
+    <tableColumn id="3" xr3:uid="{896D9B42-2273-46F8-B743-835BB97E4AE8}" name="group_size"/>
+    <tableColumn id="7" xr3:uid="{69966552-CF31-438E-8FA9-BE2A5E88FAC9}" name="P1_gender"/>
+    <tableColumn id="4" xr3:uid="{5A2E3263-D777-4053-BD11-DCC52052C267}" name="P1_mean_blink_duration_ms"/>
+    <tableColumn id="8" xr3:uid="{3D5C05A1-85E0-4094-A2D9-20563921DE31}" name="P2_gender"/>
+    <tableColumn id="5" xr3:uid="{39823323-8935-47A6-B378-D5A5BB51E7CE}" name="P2_mean_blink_duration_ms"/>
+    <tableColumn id="6" xr3:uid="{A823AD25-EA0B-45CF-9563-D312DDEA643F}" name="group_mean_blink_duration_ms"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{2720AA04-FEBA-4415-A7F3-F59E365110E9}" name="Table14" displayName="Table14" ref="L52:U66" totalsRowShown="0">
+  <autoFilter ref="L52:U66" xr:uid="{2720AA04-FEBA-4415-A7F3-F59E365110E9}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{7B463F6F-051D-4EE6-821C-15AED94CE41A}" name="group_name_short"/>
+    <tableColumn id="2" xr3:uid="{7297E81D-534F-4567-A6B8-F9BC6C880626}" name="group_name"/>
+    <tableColumn id="3" xr3:uid="{530829EC-26A8-4FF5-B449-A7D81A50FA9F}" name="group_size"/>
+    <tableColumn id="8" xr3:uid="{F2562DB2-7CA2-4FB9-905C-F25F8566CF5C}" name="P1_gender"/>
+    <tableColumn id="4" xr3:uid="{B654737D-98F9-4515-9AB7-F633720F9E57}" name="P1_mean_blink_duration_ms"/>
+    <tableColumn id="9" xr3:uid="{16D1A11B-D46F-46A0-BA16-22AD8BC6490A}" name="P2_gender"/>
+    <tableColumn id="5" xr3:uid="{24F86799-7492-4DCC-9F0A-65E612F158F4}" name="P2_mean_blink_duration_ms"/>
+    <tableColumn id="10" xr3:uid="{C5401552-A79E-4E6F-9850-CF3D2EA6C197}" name="P3_gender"/>
+    <tableColumn id="6" xr3:uid="{FD0A4B73-4A6E-499A-A9BA-EF1A6EF1C5DA}" name="P3_mean_blink_duration_ms"/>
+    <tableColumn id="7" xr3:uid="{12871194-D9ED-4A3A-9778-98BE28CAB2B1}" name="group_mean_blink_duration_ms"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{9A7F68AD-418F-431C-B9F0-FF5C5B4BEEF7}" name="Table15" displayName="Table15" ref="A68:C90" totalsRowShown="0">
+  <autoFilter ref="A68:C90" xr:uid="{9A7F68AD-418F-431C-B9F0-FF5C5B4BEEF7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A69:C90">
+    <sortCondition ref="B68:B90"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{8A6B19DA-0A67-45D7-AA5E-FBD702D4CE9E}" name="group_name_short"/>
+    <tableColumn id="2" xr3:uid="{BC75F507-7ECF-43C7-9EB3-FBD28265E747}" name="gender" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{40CDA364-0895-445E-AC23-1D8A53951A7D}" name="mean_blink_duration_ms" dataDxfId="44"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{6F2AB8C8-AB4B-4F10-9AD4-BF6972AB8A75}" name="Table16" displayName="Table16" ref="L69:N111" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42" tableBorderDxfId="41">
+  <autoFilter ref="L69:N111" xr:uid="{6F2AB8C8-AB4B-4F10-9AD4-BF6972AB8A75}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="L70:N111">
+    <sortCondition ref="M69:M111"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{ADA38E17-825F-4F62-B2BD-85835AAAB86D}" name="group_name_short" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{27F8188E-11C6-411C-B1B2-BC5C2F1E8BEC}" name="gender" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{39F8D9CA-6B6A-4D8D-95C8-36201FCE4048}" name="mean_blink_duration_ms" dataDxfId="38"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AD080257-BFA1-460B-B07A-36A64761A16A}" name="Table1" displayName="Table1" ref="C1:F12" totalsRowShown="0" dataDxfId="37">
   <autoFilter ref="C1:F12" xr:uid="{AD080257-BFA1-460B-B07A-36A64761A16A}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4F27821A-74B4-4054-BD57-59CB04F69638}" name="Group" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{40FF8A35-FADD-40F8-9C7C-8272D131492D}" name="P1" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{57E54AEA-9EE5-4960-BBF2-37C5CACE9F4B}" name="P2" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{9B5C91BC-FC38-40B1-900E-1D679A89BBE9}" name="P1_P2_AVG" dataDxfId="17">
+    <tableColumn id="1" xr3:uid="{4F27821A-74B4-4054-BD57-59CB04F69638}" name="Group" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{40FF8A35-FADD-40F8-9C7C-8272D131492D}" name="P1" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{57E54AEA-9EE5-4960-BBF2-37C5CACE9F4B}" name="P2" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{9B5C91BC-FC38-40B1-900E-1D679A89BBE9}" name="P1_P2_AVG" dataDxfId="33">
       <calculatedColumnFormula>AVERAGE(Table1[[#This Row],[P1]]:Table1[[#This Row],[P2]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16429,24 +18355,24 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1613B083-0BCB-449A-A18A-943282863FFE}" name="Table2" displayName="Table2" ref="I1:P15" totalsRowShown="0" dataDxfId="16">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1613B083-0BCB-449A-A18A-943282863FFE}" name="Table2" displayName="Table2" ref="I1:P15" totalsRowShown="0" dataDxfId="32">
   <autoFilter ref="I1:P15" xr:uid="{1613B083-0BCB-449A-A18A-943282863FFE}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{4B00F100-EEAB-4176-8F7C-64576AF95E9C}" name="Group" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{0C1C6D39-9F0B-4EFB-8FFF-6819FFEE1A73}" name="P1" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{4B646295-E6BA-4208-9890-BF77B7CC4DB0}" name="P2" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{90141FC2-ED7D-4A6B-AFC1-04A51D13EAB7}" name="P3" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{45EA91F4-80A5-4D09-8BA5-58CA8E684F50}" name="avg_P1P2" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{4B00F100-EEAB-4176-8F7C-64576AF95E9C}" name="Group" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{0C1C6D39-9F0B-4EFB-8FFF-6819FFEE1A73}" name="P1" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{4B646295-E6BA-4208-9890-BF77B7CC4DB0}" name="P2" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{90141FC2-ED7D-4A6B-AFC1-04A51D13EAB7}" name="P3" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{45EA91F4-80A5-4D09-8BA5-58CA8E684F50}" name="avg_P1P2" dataDxfId="27">
       <calculatedColumnFormula>AVERAGE(Table2[[#This Row],[P1]:[P2]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{8D95483F-1D1F-4BC0-9A13-DB0617692381}" name="avg_P1P3" dataDxfId="10">
+    <tableColumn id="6" xr3:uid="{8D95483F-1D1F-4BC0-9A13-DB0617692381}" name="avg_P1P3" dataDxfId="26">
       <calculatedColumnFormula>AVERAGE(J2,L2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{CEE85F33-BF2F-4114-920C-22ACF0374CF1}" name="avg_P2P3" dataDxfId="9">
+    <tableColumn id="7" xr3:uid="{CEE85F33-BF2F-4114-920C-22ACF0374CF1}" name="avg_P2P3" dataDxfId="25">
       <calculatedColumnFormula>AVERAGE(Table2[[#This Row],[P2]]:Table2[[#This Row],[P3]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{2974D60E-6187-4B53-9C0A-D6CCD473C533}" name="avg_P123" dataDxfId="8">
+    <tableColumn id="8" xr3:uid="{2974D60E-6187-4B53-9C0A-D6CCD473C533}" name="avg_P123" dataDxfId="24">
       <calculatedColumnFormula>AVERAGE(Table2[[#This Row],[P1]],Table2[[#This Row],[P2]],Table2[[#This Row],[P3]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16454,79 +18380,18 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2DDE5A9D-30CA-46ED-97F0-1C4FEC122E36}" name="Table3" displayName="Table3" ref="I2:M13" totalsRowShown="0">
-  <autoFilter ref="I2:M13" xr:uid="{2DDE5A9D-30CA-46ED-97F0-1C4FEC122E36}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3F2D9A49-CB8D-42DB-9308-C8C69690D536}" name="group_name"/>
-    <tableColumn id="2" xr3:uid="{52DE6ABD-824B-4973-B79D-365B55975AD4}" name="group_size"/>
-    <tableColumn id="3" xr3:uid="{F4EE57F7-134D-4B1D-A183-5A5DB8EC2A51}" name="count_blinks_participant_reference"/>
-    <tableColumn id="4" xr3:uid="{13D1FF19-31EE-4C8B-8D48-6D9C1440961D}" name="count_sync_blinks"/>
-    <tableColumn id="5" xr3:uid="{EBCD6D38-DA7A-4B32-A832-56FD5FE27505}" name="percent_sync_blinks"/>
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{9662D342-6AE4-495B-93A1-01C56177B1D4}" name="Table17" displayName="Table17" ref="B135:G146" totalsRowShown="0">
+  <autoFilter ref="B135:G146" xr:uid="{9662D342-6AE4-495B-93A1-01C56177B1D4}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{2C7EA611-DDF5-47CA-BC8F-318CF162DEFE}" name="short_group_name"/>
+    <tableColumn id="2" xr3:uid="{AC2C6434-D758-408E-BD28-0BFC9678EAA0}" name="Group"/>
+    <tableColumn id="3" xr3:uid="{25C6EAE5-3273-4462-BB48-A02E312A4DF8}" name="P1_gender"/>
+    <tableColumn id="4" xr3:uid="{D47A26C1-FEA3-4261-9C5D-82B89E11D1FA}" name="P1"/>
+    <tableColumn id="5" xr3:uid="{3712710B-57D8-448D-A7A8-AD3DA55695B3}" name="P2_gender"/>
+    <tableColumn id="6" xr3:uid="{13FAB786-3C48-4E76-ABB2-BA1F446F3140}" name="P2"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9C85DFC2-8853-442F-82F5-FC50BCDA248D}" name="Table4" displayName="Table4" ref="P2:T16" totalsRowShown="0">
-  <autoFilter ref="P2:T16" xr:uid="{9C85DFC2-8853-442F-82F5-FC50BCDA248D}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4EBA4596-D512-4014-8443-5406E0A17D40}" name="group_name"/>
-    <tableColumn id="2" xr3:uid="{6BE7A398-823C-4857-870A-1AF477ADDFF4}" name="group_size"/>
-    <tableColumn id="3" xr3:uid="{155A14E7-67CE-47D1-ABCB-DA40DBA3CD30}" name="count_blinks_participant_reference"/>
-    <tableColumn id="4" xr3:uid="{7A67B0EE-5289-48DB-8223-9B55BE9C9BCB}" name="count_sync_blinks"/>
-    <tableColumn id="5" xr3:uid="{7D7D6422-F269-4D6B-ACA7-3BF34AF789DD}" name="percent_sync_blinks"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8C25D1AD-2854-40AA-8354-72C5021373BA}" name="Table5" displayName="Table5" ref="G1:J12" totalsRowShown="0">
-  <autoFilter ref="G1:J12" xr:uid="{8C25D1AD-2854-40AA-8354-72C5021373BA}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{6D40A87A-BB4C-4E8C-B2B2-45A314637EAB}" name="group_name"/>
-    <tableColumn id="2" xr3:uid="{44B8A537-3D3D-4A32-A4E9-A479A2FBAEB8}" name="group_size"/>
-    <tableColumn id="3" xr3:uid="{E56604FE-4744-4494-96E9-2E228A162AAB}" name="count_sync_blinks"/>
-    <tableColumn id="4" xr3:uid="{23F049FC-98FA-4630-A819-6E88CF2BB14F}" name="avg_blinks_async_ms"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{F064CA2C-1F70-44B8-BBA9-1279DE17B6FA}" name="Table6" displayName="Table6" ref="N1:Q15" totalsRowShown="0">
-  <autoFilter ref="N1:Q15" xr:uid="{F064CA2C-1F70-44B8-BBA9-1279DE17B6FA}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5590ACE3-601B-4874-B2FD-40E7CE33D13C}" name="group_name"/>
-    <tableColumn id="2" xr3:uid="{DBD04632-1B48-46B6-8176-FBFC5676F488}" name="group_size"/>
-    <tableColumn id="3" xr3:uid="{E2EF6420-C922-43B5-A67E-B09B3D8CAC04}" name="count_sync_blinks"/>
-    <tableColumn id="4" xr3:uid="{C1FE3794-32D2-4348-A14B-DA8E4EC94C43}" name="avg_blinks_async_ms"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{87D36C7E-4AD2-425A-BAE4-7F65D68961B3}" name="Table9" displayName="Table9" ref="B2:N13" totalsRowShown="0">
-  <autoFilter ref="B2:N13" xr:uid="{87D36C7E-4AD2-425A-BAE4-7F65D68961B3}"/>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{9BC1567B-64A2-4977-B462-E55CD1930503}" name="group index"/>
-    <tableColumn id="2" xr3:uid="{22340563-374A-41E8-9D56-C75D1890ED3F}" name="-1500"/>
-    <tableColumn id="3" xr3:uid="{1FF8687A-8105-4FD8-BEA2-D5AB4CC51840}" name="-1250"/>
-    <tableColumn id="4" xr3:uid="{351898DC-892A-48D0-BC44-899BCD29B003}" name="-1000"/>
-    <tableColumn id="5" xr3:uid="{10ABA271-061E-4E25-93AA-23D298B61FA2}" name="-750"/>
-    <tableColumn id="6" xr3:uid="{A8A1DE2D-6ACD-4369-A468-5E4751A4E065}" name="-500"/>
-    <tableColumn id="7" xr3:uid="{1D598D59-4409-4DA8-B18C-34B02FFF856B}" name="-250"/>
-    <tableColumn id="8" xr3:uid="{D541AF2B-E7C2-471F-AFF0-AD9BCA3B328A}" name="0"/>
-    <tableColumn id="9" xr3:uid="{F633A798-9031-42A6-9031-A0988867361C}" name="250"/>
-    <tableColumn id="10" xr3:uid="{321CCB05-D4C5-4E13-B6C6-D0D29029B8CA}" name="500"/>
-    <tableColumn id="11" xr3:uid="{64A44B7D-08D9-4B98-9EF3-E5A3A28326A0}" name="750"/>
-    <tableColumn id="12" xr3:uid="{485F7809-F3B6-4A67-8541-C8D4A372FC10}" name="1000"/>
-    <tableColumn id="13" xr3:uid="{8F82B826-F05C-4ED9-AB02-311044D91A11}" name="1250"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -16794,13 +18659,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G44"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="54.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
-    <col min="3" max="3" width="27.54296875" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" customWidth="1"/>
-    <col min="5" max="5" width="11.54296875" customWidth="1"/>
+    <col min="1" max="1" width="54.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -17362,23 +19227,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED3C3795-97EB-4298-A25F-860B0A0E50BA}">
-  <dimension ref="B1:N44"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:W117"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.26953125" customWidth="1"/>
-    <col min="2" max="2" width="23.81640625" customWidth="1"/>
-    <col min="3" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
-    <col min="10" max="10" width="11.81640625" customWidth="1"/>
-    <col min="11" max="11" width="14.26953125" customWidth="1"/>
-    <col min="12" max="12" width="9.7265625" customWidth="1"/>
-    <col min="13" max="13" width="27.1796875" customWidth="1"/>
-    <col min="14" max="14" width="30.1796875" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="9" max="9" width="53.42578125" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" customWidth="1"/>
+    <col min="12" max="12" width="19.85546875" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="14" max="14" width="25.7109375" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" customWidth="1"/>
+    <col min="16" max="16" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.85546875" customWidth="1"/>
+    <col min="18" max="18" width="12.85546875" customWidth="1"/>
+    <col min="19" max="19" width="13.85546875" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="34.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14">
+    <row r="1" spans="1:14">
+      <c r="A1" t="s">
+        <v>235</v>
+      </c>
       <c r="B1" t="s">
         <v>163</v>
       </c>
@@ -17394,6 +19271,9 @@
       <c r="F1" t="s">
         <v>168</v>
       </c>
+      <c r="H1" t="s">
+        <v>235</v>
+      </c>
       <c r="I1" t="s">
         <v>163</v>
       </c>
@@ -17413,7 +19293,10 @@
         <v>168</v>
       </c>
     </row>
-    <row r="2" spans="2:14">
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>236</v>
+      </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
@@ -17429,6 +19312,9 @@
       <c r="F2">
         <v>165.584834</v>
       </c>
+      <c r="H2" t="s">
+        <v>247</v>
+      </c>
       <c r="I2" t="s">
         <v>66</v>
       </c>
@@ -17448,7 +19334,10 @@
         <v>170.73056800000001</v>
       </c>
     </row>
-    <row r="3" spans="2:14">
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>237</v>
+      </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
@@ -17464,6 +19353,9 @@
       <c r="F3">
         <v>239.006179</v>
       </c>
+      <c r="H3" t="s">
+        <v>249</v>
+      </c>
       <c r="I3" t="s">
         <v>68</v>
       </c>
@@ -17483,7 +19375,10 @@
         <v>183.88859099999999</v>
       </c>
     </row>
-    <row r="4" spans="2:14">
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>238</v>
+      </c>
       <c r="B4" t="s">
         <v>62</v>
       </c>
@@ -17499,6 +19394,9 @@
       <c r="F4">
         <v>183.71825000000001</v>
       </c>
+      <c r="H4" t="s">
+        <v>250</v>
+      </c>
       <c r="I4" t="s">
         <v>69</v>
       </c>
@@ -17518,7 +19416,10 @@
         <v>156.64345900000001</v>
       </c>
     </row>
-    <row r="5" spans="2:14">
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>239</v>
+      </c>
       <c r="B5" t="s">
         <v>61</v>
       </c>
@@ -17534,6 +19435,9 @@
       <c r="F5">
         <v>165.76065500000001</v>
       </c>
+      <c r="H5" t="s">
+        <v>251</v>
+      </c>
       <c r="I5" t="s">
         <v>70</v>
       </c>
@@ -17553,7 +19457,10 @@
         <v>173.16583900000001</v>
       </c>
     </row>
-    <row r="6" spans="2:14">
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>240</v>
+      </c>
       <c r="B6" t="s">
         <v>59</v>
       </c>
@@ -17569,6 +19476,9 @@
       <c r="F6">
         <v>215.91097500000001</v>
       </c>
+      <c r="H6" t="s">
+        <v>252</v>
+      </c>
       <c r="I6" t="s">
         <v>71</v>
       </c>
@@ -17588,7 +19498,10 @@
         <v>181.58262199999999</v>
       </c>
     </row>
-    <row r="7" spans="2:14">
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>241</v>
+      </c>
       <c r="B7" t="s">
         <v>58</v>
       </c>
@@ -17604,6 +19517,9 @@
       <c r="F7">
         <v>197.96016700000001</v>
       </c>
+      <c r="H7" t="s">
+        <v>253</v>
+      </c>
       <c r="I7" t="s">
         <v>73</v>
       </c>
@@ -17623,7 +19539,10 @@
         <v>184.48833400000001</v>
       </c>
     </row>
-    <row r="8" spans="2:14">
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>242</v>
+      </c>
       <c r="B8" t="s">
         <v>57</v>
       </c>
@@ -17639,6 +19558,9 @@
       <c r="F8">
         <v>174.439739</v>
       </c>
+      <c r="H8" t="s">
+        <v>254</v>
+      </c>
       <c r="I8" t="s">
         <v>74</v>
       </c>
@@ -17658,7 +19580,10 @@
         <v>181.230921</v>
       </c>
     </row>
-    <row r="9" spans="2:14">
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>243</v>
+      </c>
       <c r="B9" t="s">
         <v>56</v>
       </c>
@@ -17674,6 +19599,9 @@
       <c r="F9">
         <v>175.91063800000001</v>
       </c>
+      <c r="H9" t="s">
+        <v>255</v>
+      </c>
       <c r="I9" t="s">
         <v>75</v>
       </c>
@@ -17693,7 +19621,10 @@
         <v>196.51147900000001</v>
       </c>
     </row>
-    <row r="10" spans="2:14">
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>244</v>
+      </c>
       <c r="B10" t="s">
         <v>55</v>
       </c>
@@ -17709,6 +19640,9 @@
       <c r="F10">
         <v>172.75160700000001</v>
       </c>
+      <c r="H10" t="s">
+        <v>248</v>
+      </c>
       <c r="I10" t="s">
         <v>49</v>
       </c>
@@ -17728,7 +19662,10 @@
         <v>186.96391800000001</v>
       </c>
     </row>
-    <row r="11" spans="2:14">
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>245</v>
+      </c>
       <c r="B11" t="s">
         <v>54</v>
       </c>
@@ -17744,6 +19681,9 @@
       <c r="F11">
         <v>212.16843700000001</v>
       </c>
+      <c r="H11" t="s">
+        <v>257</v>
+      </c>
       <c r="I11" t="s">
         <v>154</v>
       </c>
@@ -17763,7 +19703,10 @@
         <v>180.33811399999999</v>
       </c>
     </row>
-    <row r="12" spans="2:14">
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>246</v>
+      </c>
       <c r="B12" t="s">
         <v>157</v>
       </c>
@@ -17779,6 +19722,9 @@
       <c r="F12">
         <v>182.27193</v>
       </c>
+      <c r="H12" t="s">
+        <v>256</v>
+      </c>
       <c r="I12" t="s">
         <v>155</v>
       </c>
@@ -17798,7 +19744,10 @@
         <v>171.38507200000001</v>
       </c>
     </row>
-    <row r="13" spans="2:14">
+    <row r="13" spans="1:14">
+      <c r="H13" t="s">
+        <v>260</v>
+      </c>
       <c r="I13" t="s">
         <v>156</v>
       </c>
@@ -17818,7 +19767,10 @@
         <v>174.51295300000001</v>
       </c>
     </row>
-    <row r="14" spans="2:14">
+    <row r="14" spans="1:14">
+      <c r="H14" t="s">
+        <v>258</v>
+      </c>
       <c r="I14" t="s">
         <v>158</v>
       </c>
@@ -17838,7 +19790,10 @@
         <v>195.46240599999999</v>
       </c>
     </row>
-    <row r="15" spans="2:14">
+    <row r="15" spans="1:14">
+      <c r="H15" t="s">
+        <v>259</v>
+      </c>
       <c r="I15" t="s">
         <v>159</v>
       </c>
@@ -17858,7 +19813,7 @@
         <v>161.57207</v>
       </c>
     </row>
-    <row r="16" spans="2:14">
+    <row r="16" spans="1:14">
       <c r="C16" t="s">
         <v>169</v>
       </c>
@@ -17924,7 +19879,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="27" spans="3:12" ht="15" thickBot="1"/>
+    <row r="27" spans="3:12" ht="15.75" thickBot="1"/>
     <row r="28" spans="3:12">
       <c r="D28" s="4"/>
       <c r="E28" s="4" t="s">
@@ -18046,7 +20001,7 @@
         <v>1.4291769235957907</v>
       </c>
     </row>
-    <row r="35" spans="2:12" ht="15" thickBot="1">
+    <row r="35" spans="2:12" ht="15.75" thickBot="1">
       <c r="D35" s="3" t="s">
         <v>162</v>
       </c>
@@ -18077,7 +20032,7 @@
         <v>0.17488621060546347</v>
       </c>
     </row>
-    <row r="38" spans="2:12" ht="15" thickBot="1">
+    <row r="38" spans="2:12" ht="15.75" thickBot="1">
       <c r="J38" s="3" t="s">
         <v>108</v>
       </c>
@@ -18091,31 +20046,2137 @@
         <v>189.58940100000001</v>
       </c>
     </row>
+    <row r="51" spans="1:21">
+      <c r="A51" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="O51" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>266</v>
+      </c>
+      <c r="S51" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
+      <c r="L52" t="s">
+        <v>235</v>
+      </c>
+      <c r="M52" t="s">
+        <v>163</v>
+      </c>
+      <c r="N52" t="s">
+        <v>165</v>
+      </c>
+      <c r="O52" t="s">
+        <v>262</v>
+      </c>
+      <c r="P52" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>263</v>
+      </c>
+      <c r="R52" t="s">
+        <v>167</v>
+      </c>
+      <c r="S52" t="s">
+        <v>264</v>
+      </c>
+      <c r="T52" t="s">
+        <v>164</v>
+      </c>
+      <c r="U52" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
+      <c r="A53" t="s">
+        <v>235</v>
+      </c>
+      <c r="B53" t="s">
+        <v>163</v>
+      </c>
+      <c r="C53" t="s">
+        <v>165</v>
+      </c>
+      <c r="D53" t="s">
+        <v>262</v>
+      </c>
+      <c r="E53" t="s">
+        <v>166</v>
+      </c>
+      <c r="F53" t="s">
+        <v>263</v>
+      </c>
+      <c r="G53" t="s">
+        <v>167</v>
+      </c>
+      <c r="H53" t="s">
+        <v>168</v>
+      </c>
+      <c r="L53" t="s">
+        <v>247</v>
+      </c>
+      <c r="M53" t="s">
+        <v>66</v>
+      </c>
+      <c r="N53">
+        <v>3</v>
+      </c>
+      <c r="O53" t="s">
+        <v>128</v>
+      </c>
+      <c r="P53">
+        <v>192.61988299999999</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>170</v>
+      </c>
+      <c r="R53">
+        <v>153.51952</v>
+      </c>
+      <c r="S53" t="s">
+        <v>128</v>
+      </c>
+      <c r="T53">
+        <v>166.052301</v>
+      </c>
+      <c r="U53">
+        <v>170.73056800000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
+      <c r="A54" t="s">
+        <v>236</v>
+      </c>
+      <c r="B54" t="s">
+        <v>65</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54" t="s">
+        <v>128</v>
+      </c>
+      <c r="E54">
+        <v>155.283019</v>
+      </c>
+      <c r="F54" t="s">
+        <v>128</v>
+      </c>
+      <c r="G54">
+        <v>175.88665</v>
+      </c>
+      <c r="H54">
+        <v>165.584834</v>
+      </c>
+      <c r="L54" t="s">
+        <v>249</v>
+      </c>
+      <c r="M54" t="s">
+        <v>68</v>
+      </c>
+      <c r="N54">
+        <v>3</v>
+      </c>
+      <c r="O54" t="s">
+        <v>128</v>
+      </c>
+      <c r="P54">
+        <v>140.052885</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>128</v>
+      </c>
+      <c r="R54">
+        <v>175.77197799999999</v>
+      </c>
+      <c r="S54" t="s">
+        <v>128</v>
+      </c>
+      <c r="T54">
+        <v>235.84090900000001</v>
+      </c>
+      <c r="U54">
+        <v>183.88859099999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21">
+      <c r="A55" t="s">
+        <v>237</v>
+      </c>
+      <c r="B55" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+      <c r="D55" t="s">
+        <v>170</v>
+      </c>
+      <c r="E55">
+        <v>218.36752100000001</v>
+      </c>
+      <c r="F55" t="s">
+        <v>128</v>
+      </c>
+      <c r="G55">
+        <v>259.644836</v>
+      </c>
+      <c r="H55">
+        <v>239.006179</v>
+      </c>
+      <c r="L55" t="s">
+        <v>250</v>
+      </c>
+      <c r="M55" t="s">
+        <v>69</v>
+      </c>
+      <c r="N55">
+        <v>3</v>
+      </c>
+      <c r="O55" t="s">
+        <v>128</v>
+      </c>
+      <c r="P55">
+        <v>125.67857100000001</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>170</v>
+      </c>
+      <c r="R55">
+        <v>171.88356200000001</v>
+      </c>
+      <c r="S55" t="s">
+        <v>128</v>
+      </c>
+      <c r="T55">
+        <v>172.36824300000001</v>
+      </c>
+      <c r="U55">
+        <v>156.64345900000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
+      <c r="A56" t="s">
+        <v>238</v>
+      </c>
+      <c r="B56" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+      <c r="D56" t="s">
+        <v>128</v>
+      </c>
+      <c r="E56">
+        <v>204.75380699999999</v>
+      </c>
+      <c r="F56" t="s">
+        <v>128</v>
+      </c>
+      <c r="G56">
+        <v>162.682692</v>
+      </c>
+      <c r="H56">
+        <v>183.71825000000001</v>
+      </c>
+      <c r="L56" t="s">
+        <v>251</v>
+      </c>
+      <c r="M56" t="s">
+        <v>70</v>
+      </c>
+      <c r="N56">
+        <v>3</v>
+      </c>
+      <c r="O56" t="s">
+        <v>128</v>
+      </c>
+      <c r="P56">
+        <v>197.77333300000001</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>128</v>
+      </c>
+      <c r="R56">
+        <v>165.45217400000001</v>
+      </c>
+      <c r="S56" t="s">
+        <v>128</v>
+      </c>
+      <c r="T56">
+        <v>156.27201099999999</v>
+      </c>
+      <c r="U56">
+        <v>173.16583900000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
+      <c r="A57" t="s">
+        <v>239</v>
+      </c>
+      <c r="B57" t="s">
+        <v>61</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+      <c r="D57" t="s">
+        <v>128</v>
+      </c>
+      <c r="E57">
+        <v>155.45097999999999</v>
+      </c>
+      <c r="F57" t="s">
+        <v>128</v>
+      </c>
+      <c r="G57">
+        <v>176.07033000000001</v>
+      </c>
+      <c r="H57">
+        <v>165.76065500000001</v>
+      </c>
+      <c r="L57" t="s">
+        <v>252</v>
+      </c>
+      <c r="M57" t="s">
+        <v>71</v>
+      </c>
+      <c r="N57">
+        <v>3</v>
+      </c>
+      <c r="O57" t="s">
+        <v>128</v>
+      </c>
+      <c r="P57">
+        <v>148.419355</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>128</v>
+      </c>
+      <c r="R57">
+        <v>213.963964</v>
+      </c>
+      <c r="S57" t="s">
+        <v>128</v>
+      </c>
+      <c r="T57">
+        <v>182.36454800000001</v>
+      </c>
+      <c r="U57">
+        <v>181.58262199999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21">
+      <c r="A58" t="s">
+        <v>240</v>
+      </c>
+      <c r="B58" t="s">
+        <v>59</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="D58" t="s">
+        <v>170</v>
+      </c>
+      <c r="E58">
+        <v>241.208955</v>
+      </c>
+      <c r="F58" t="s">
+        <v>170</v>
+      </c>
+      <c r="G58">
+        <v>190.61299399999999</v>
+      </c>
+      <c r="H58">
+        <v>215.91097500000001</v>
+      </c>
+      <c r="L58" t="s">
+        <v>253</v>
+      </c>
+      <c r="M58" t="s">
+        <v>73</v>
+      </c>
+      <c r="N58">
+        <v>3</v>
+      </c>
+      <c r="O58" t="s">
+        <v>128</v>
+      </c>
+      <c r="P58">
+        <v>133.942857</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>128</v>
+      </c>
+      <c r="R58">
+        <v>253.12820500000001</v>
+      </c>
+      <c r="S58" t="s">
+        <v>128</v>
+      </c>
+      <c r="T58">
+        <v>166.39393899999999</v>
+      </c>
+      <c r="U58">
+        <v>184.48833400000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
+      <c r="A59" t="s">
+        <v>241</v>
+      </c>
+      <c r="B59" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+      <c r="D59" t="s">
+        <v>170</v>
+      </c>
+      <c r="E59">
+        <v>210.85906</v>
+      </c>
+      <c r="F59" t="s">
+        <v>128</v>
+      </c>
+      <c r="G59">
+        <v>185.06127499999999</v>
+      </c>
+      <c r="H59">
+        <v>197.96016700000001</v>
+      </c>
+      <c r="L59" t="s">
+        <v>254</v>
+      </c>
+      <c r="M59" t="s">
+        <v>74</v>
+      </c>
+      <c r="N59">
+        <v>3</v>
+      </c>
+      <c r="O59" t="s">
+        <v>128</v>
+      </c>
+      <c r="P59">
+        <v>206.78022000000001</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>170</v>
+      </c>
+      <c r="R59">
+        <v>174.05384599999999</v>
+      </c>
+      <c r="S59" t="s">
+        <v>128</v>
+      </c>
+      <c r="T59">
+        <v>162.85869600000001</v>
+      </c>
+      <c r="U59">
+        <v>181.230921</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21">
+      <c r="A60" t="s">
+        <v>242</v>
+      </c>
+      <c r="B60" t="s">
+        <v>57</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60" t="s">
+        <v>170</v>
+      </c>
+      <c r="E60">
+        <v>193.80620200000001</v>
+      </c>
+      <c r="F60" t="s">
+        <v>170</v>
+      </c>
+      <c r="G60">
+        <v>155.07327599999999</v>
+      </c>
+      <c r="H60">
+        <v>174.439739</v>
+      </c>
+      <c r="L60" t="s">
+        <v>255</v>
+      </c>
+      <c r="M60" t="s">
+        <v>75</v>
+      </c>
+      <c r="N60">
+        <v>3</v>
+      </c>
+      <c r="O60" t="s">
+        <v>128</v>
+      </c>
+      <c r="P60">
+        <v>170.885965</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>128</v>
+      </c>
+      <c r="R60">
+        <v>240.30364399999999</v>
+      </c>
+      <c r="S60" t="s">
+        <v>128</v>
+      </c>
+      <c r="T60">
+        <v>178.34482800000001</v>
+      </c>
+      <c r="U60">
+        <v>196.51147900000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21">
+      <c r="A61" t="s">
+        <v>243</v>
+      </c>
+      <c r="B61" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="D61" t="s">
+        <v>170</v>
+      </c>
+      <c r="E61">
+        <v>158.79097400000001</v>
+      </c>
+      <c r="F61" t="s">
+        <v>128</v>
+      </c>
+      <c r="G61">
+        <v>193.030303</v>
+      </c>
+      <c r="H61">
+        <v>175.91063800000001</v>
+      </c>
+      <c r="L61" t="s">
+        <v>248</v>
+      </c>
+      <c r="M61" t="s">
+        <v>49</v>
+      </c>
+      <c r="N61">
+        <v>3</v>
+      </c>
+      <c r="O61" t="s">
+        <v>128</v>
+      </c>
+      <c r="P61">
+        <v>190.14367799999999</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>170</v>
+      </c>
+      <c r="R61">
+        <v>176.79674800000001</v>
+      </c>
+      <c r="S61" t="s">
+        <v>128</v>
+      </c>
+      <c r="T61">
+        <v>193.95132699999999</v>
+      </c>
+      <c r="U61">
+        <v>186.96391800000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21">
+      <c r="A62" t="s">
+        <v>244</v>
+      </c>
+      <c r="B62" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62" t="s">
+        <v>128</v>
+      </c>
+      <c r="E62">
+        <v>159.34567899999999</v>
+      </c>
+      <c r="F62" t="s">
+        <v>128</v>
+      </c>
+      <c r="G62">
+        <v>186.157534</v>
+      </c>
+      <c r="H62">
+        <v>172.75160700000001</v>
+      </c>
+      <c r="L62" t="s">
+        <v>257</v>
+      </c>
+      <c r="M62" t="s">
+        <v>154</v>
+      </c>
+      <c r="N62">
+        <v>3</v>
+      </c>
+      <c r="O62" t="s">
+        <v>170</v>
+      </c>
+      <c r="P62">
+        <v>149.02941200000001</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>128</v>
+      </c>
+      <c r="R62">
+        <v>165.265152</v>
+      </c>
+      <c r="S62" t="s">
+        <v>128</v>
+      </c>
+      <c r="T62">
+        <v>226.71977999999999</v>
+      </c>
+      <c r="U62">
+        <v>180.33811399999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21">
+      <c r="A63" t="s">
+        <v>245</v>
+      </c>
+      <c r="B63" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63" t="s">
+        <v>170</v>
+      </c>
+      <c r="E63">
+        <v>233.86496399999999</v>
+      </c>
+      <c r="F63" t="s">
+        <v>170</v>
+      </c>
+      <c r="G63">
+        <v>190.47191000000001</v>
+      </c>
+      <c r="H63">
+        <v>212.16843700000001</v>
+      </c>
+      <c r="L63" t="s">
+        <v>256</v>
+      </c>
+      <c r="M63" t="s">
+        <v>155</v>
+      </c>
+      <c r="N63">
+        <v>3</v>
+      </c>
+      <c r="O63" t="s">
+        <v>170</v>
+      </c>
+      <c r="P63">
+        <v>179.045455</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>170</v>
+      </c>
+      <c r="R63">
+        <v>181.13793100000001</v>
+      </c>
+      <c r="S63" t="s">
+        <v>128</v>
+      </c>
+      <c r="T63">
+        <v>153.97183100000001</v>
+      </c>
+      <c r="U63">
+        <v>171.38507200000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21">
+      <c r="A64" t="s">
+        <v>246</v>
+      </c>
+      <c r="B64" t="s">
+        <v>157</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+      <c r="D64" t="s">
+        <v>170</v>
+      </c>
+      <c r="E64">
+        <v>162.87719300000001</v>
+      </c>
+      <c r="F64" t="s">
+        <v>170</v>
+      </c>
+      <c r="G64">
+        <v>201.66666699999999</v>
+      </c>
+      <c r="H64">
+        <v>182.27193</v>
+      </c>
+      <c r="L64" t="s">
+        <v>260</v>
+      </c>
+      <c r="M64" t="s">
+        <v>156</v>
+      </c>
+      <c r="N64">
+        <v>3</v>
+      </c>
+      <c r="O64" t="s">
+        <v>128</v>
+      </c>
+      <c r="P64">
+        <v>155.252137</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>128</v>
+      </c>
+      <c r="R64">
+        <v>194.52795</v>
+      </c>
+      <c r="S64" t="s">
+        <v>170</v>
+      </c>
+      <c r="T64">
+        <v>173.75877199999999</v>
+      </c>
+      <c r="U64">
+        <v>174.51295300000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23">
+      <c r="L65" t="s">
+        <v>258</v>
+      </c>
+      <c r="M65" t="s">
+        <v>158</v>
+      </c>
+      <c r="N65">
+        <v>3</v>
+      </c>
+      <c r="O65" t="s">
+        <v>170</v>
+      </c>
+      <c r="P65">
+        <v>190.340136</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>170</v>
+      </c>
+      <c r="R65">
+        <v>168.39919399999999</v>
+      </c>
+      <c r="S65" t="s">
+        <v>170</v>
+      </c>
+      <c r="T65">
+        <v>227.647887</v>
+      </c>
+      <c r="U65">
+        <v>195.46240599999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23">
+      <c r="L66" t="s">
+        <v>259</v>
+      </c>
+      <c r="M66" t="s">
+        <v>159</v>
+      </c>
+      <c r="N66">
+        <v>3</v>
+      </c>
+      <c r="O66" t="s">
+        <v>128</v>
+      </c>
+      <c r="P66">
+        <v>150.79701499999999</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>128</v>
+      </c>
+      <c r="R66">
+        <v>156.904977</v>
+      </c>
+      <c r="S66" t="s">
+        <v>170</v>
+      </c>
+      <c r="T66">
+        <v>177.014218</v>
+      </c>
+      <c r="U66">
+        <v>161.57207</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23">
+      <c r="A68" t="s">
+        <v>235</v>
+      </c>
+      <c r="B68" t="s">
+        <v>270</v>
+      </c>
+      <c r="C68" t="s">
+        <v>271</v>
+      </c>
+      <c r="E68" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="F68" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23">
+      <c r="A69" t="s">
+        <v>236</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C69" s="20">
+        <v>155.283019</v>
+      </c>
+      <c r="E69" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="F69">
+        <v>183.03337318181818</v>
+      </c>
+      <c r="L69" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="M69" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="N69" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="P69" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23">
+      <c r="A70" t="s">
+        <v>238</v>
+      </c>
+      <c r="B70" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C70" s="20">
+        <v>204.75380699999999</v>
+      </c>
+      <c r="E70" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="F70">
+        <v>196.14542872727273</v>
+      </c>
+      <c r="L70" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="M70" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N70" s="20">
+        <v>192.61988299999999</v>
+      </c>
+      <c r="P70" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q70">
+        <v>179.09341186666663</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23">
+      <c r="A71" t="s">
+        <v>239</v>
+      </c>
+      <c r="B71" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C71" s="20">
+        <v>155.45097999999999</v>
+      </c>
+      <c r="E71" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="F71">
+        <v>189.58940095454548</v>
+      </c>
+      <c r="L71" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="M71" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N71" s="20">
+        <v>140.052885</v>
+      </c>
+      <c r="P71" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q71">
+        <v>176.88555675000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23">
+      <c r="A72" t="s">
+        <v>244</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C72" s="20">
+        <v>159.34567899999999</v>
+      </c>
+      <c r="L72" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="M72" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N72" s="20">
+        <v>125.67857100000001</v>
+      </c>
+      <c r="P72" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q72">
+        <v>178.46259611904759</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23">
+      <c r="A73" t="s">
+        <v>236</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C73" s="20">
+        <v>175.88665</v>
+      </c>
+      <c r="L73" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="M73" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N73" s="20">
+        <v>197.77333300000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23">
+      <c r="A74" t="s">
+        <v>237</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C74" s="20">
+        <v>259.644836</v>
+      </c>
+      <c r="E74" t="s">
+        <v>109</v>
+      </c>
+      <c r="I74" t="s">
+        <v>160</v>
+      </c>
+      <c r="L74" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="M74" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N74" s="20">
+        <v>148.419355</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A75" t="s">
+        <v>238</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C75" s="20">
+        <v>162.682692</v>
+      </c>
+      <c r="F75" t="s">
+        <v>128</v>
+      </c>
+      <c r="G75" t="s">
+        <v>170</v>
+      </c>
+      <c r="L75" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="M75" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N75" s="20">
+        <v>133.942857</v>
+      </c>
+      <c r="P75" t="s">
+        <v>109</v>
+      </c>
+      <c r="U75" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A76" t="s">
+        <v>239</v>
+      </c>
+      <c r="B76" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C76" s="20">
+        <v>176.07033000000001</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I76" s="33"/>
+      <c r="J76" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="K76" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="L76" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="M76" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N76" s="20">
+        <v>206.78022000000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23">
+      <c r="A77" t="s">
+        <v>241</v>
+      </c>
+      <c r="B77" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C77" s="20">
+        <v>185.06127499999999</v>
+      </c>
+      <c r="E77" t="s">
+        <v>99</v>
+      </c>
+      <c r="F77">
+        <v>183.03337318181818</v>
+      </c>
+      <c r="G77">
+        <v>196.14542872727273</v>
+      </c>
+      <c r="I77" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="J77" s="31">
+        <v>183.03337318181818</v>
+      </c>
+      <c r="K77" s="31">
+        <v>196.14542872727273</v>
+      </c>
+      <c r="L77" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="M77" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N77" s="20">
+        <v>170.885965</v>
+      </c>
+      <c r="P77" s="33"/>
+      <c r="Q77" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="R77" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="U77" s="33"/>
+      <c r="V77" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="W77" s="33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23">
+      <c r="A78" t="s">
+        <v>243</v>
+      </c>
+      <c r="B78" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C78" s="20">
+        <v>193.030303</v>
+      </c>
+      <c r="E78" t="s">
+        <v>100</v>
+      </c>
+      <c r="F78">
+        <v>906.05921264408391</v>
+      </c>
+      <c r="G78">
+        <v>845.16023000663847</v>
+      </c>
+      <c r="I78" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="J78" s="31">
+        <v>906.05921264408391</v>
+      </c>
+      <c r="K78" s="31">
+        <v>845.16023000663847</v>
+      </c>
+      <c r="L78" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="M78" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N78" s="20">
+        <v>190.14367799999999</v>
+      </c>
+      <c r="P78" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q78" s="31">
+        <v>179.09341186666663</v>
+      </c>
+      <c r="R78" s="31">
+        <v>176.88555675000001</v>
+      </c>
+      <c r="U78" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="V78" s="31">
+        <v>179.09341186666663</v>
+      </c>
+      <c r="W78" s="31">
+        <v>176.88555675000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23">
+      <c r="A79" t="s">
+        <v>244</v>
+      </c>
+      <c r="B79" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C79" s="22">
+        <v>186.157534</v>
+      </c>
+      <c r="E79" t="s">
+        <v>101</v>
+      </c>
+      <c r="F79">
+        <v>11</v>
+      </c>
+      <c r="G79">
+        <v>11</v>
+      </c>
+      <c r="I79" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="J79" s="31">
+        <v>11</v>
+      </c>
+      <c r="K79" s="31">
+        <v>11</v>
+      </c>
+      <c r="L79" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="M79" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N79" s="20">
+        <v>155.252137</v>
+      </c>
+      <c r="P79" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q79" s="31">
+        <v>1009.9693357996152</v>
+      </c>
+      <c r="R79" s="31">
+        <v>383.39839179197389</v>
+      </c>
+      <c r="U79" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="V79" s="31">
+        <v>1009.9693357996152</v>
+      </c>
+      <c r="W79" s="31">
+        <v>383.39839179197389</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23">
+      <c r="A80" t="s">
+        <v>237</v>
+      </c>
+      <c r="B80" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C80" s="20">
+        <v>218.36752100000001</v>
+      </c>
+      <c r="E80" t="s">
+        <v>110</v>
+      </c>
+      <c r="F80">
+        <v>875.60972132536119</v>
+      </c>
+      <c r="I80" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="J80" s="31">
+        <v>10</v>
+      </c>
+      <c r="K80" s="31">
+        <v>10</v>
+      </c>
+      <c r="L80" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="M80" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N80" s="20">
+        <v>150.79701499999999</v>
+      </c>
+      <c r="P80" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q80" s="31">
+        <v>30</v>
+      </c>
+      <c r="R80" s="31">
+        <v>12</v>
+      </c>
+      <c r="U80" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="V80" s="31">
+        <v>30</v>
+      </c>
+      <c r="W80" s="31">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23">
+      <c r="A81" t="s">
+        <v>240</v>
+      </c>
+      <c r="B81" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C81" s="20">
+        <v>241.208955</v>
+      </c>
+      <c r="E81" t="s">
+        <v>102</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="I81" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="J81" s="31">
+        <v>1.0720561385584448</v>
+      </c>
+      <c r="K81" s="31"/>
+      <c r="L81" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="M81" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N81" s="20">
+        <v>175.77197799999999</v>
+      </c>
+      <c r="P81" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q81" s="31">
+        <v>837.66232619751395</v>
+      </c>
+      <c r="R81" s="31"/>
+      <c r="U81" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="V81" s="31">
+        <v>29</v>
+      </c>
+      <c r="W81" s="31">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23">
+      <c r="A82" t="s">
+        <v>241</v>
+      </c>
+      <c r="B82" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C82" s="20">
+        <v>210.85906</v>
+      </c>
+      <c r="E82" t="s">
+        <v>103</v>
+      </c>
+      <c r="F82">
+        <v>20</v>
+      </c>
+      <c r="I82" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="J82" s="31">
+        <v>0.45727913976215517</v>
+      </c>
+      <c r="K82" s="31"/>
+      <c r="L82" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="M82" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N82" s="20">
+        <v>165.45217400000001</v>
+      </c>
+      <c r="P82" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q82" s="31">
+        <v>0</v>
+      </c>
+      <c r="R82" s="31"/>
+      <c r="U82" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="V82" s="31">
+        <v>2.634255535290845</v>
+      </c>
+      <c r="W82" s="31"/>
+    </row>
+    <row r="83" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A83" t="s">
+        <v>242</v>
+      </c>
+      <c r="B83" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C83" s="20">
+        <v>193.80620200000001</v>
+      </c>
+      <c r="E83" t="s">
+        <v>104</v>
+      </c>
+      <c r="F83">
+        <v>-1.0391944957649899</v>
+      </c>
+      <c r="I83" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="J83" s="32">
+        <v>2.9782370160823217</v>
+      </c>
+      <c r="K83" s="32"/>
+      <c r="L83" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="M83" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="N83" s="22">
+        <v>213.963964</v>
+      </c>
+      <c r="P83" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q83" s="31">
+        <v>40</v>
+      </c>
+      <c r="R83" s="31"/>
+      <c r="U83" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="V83" s="31">
+        <v>4.6282415342331011E-2</v>
+      </c>
+      <c r="W83" s="31"/>
+    </row>
+    <row r="84" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A84" t="s">
+        <v>243</v>
+      </c>
+      <c r="B84" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C84" s="20">
+        <v>158.79097400000001</v>
+      </c>
+      <c r="E84" t="s">
+        <v>105</v>
+      </c>
+      <c r="F84">
+        <v>0.15555763498771033</v>
+      </c>
+      <c r="L84" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="M84" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N84" s="20">
+        <v>253.12820500000001</v>
+      </c>
+      <c r="P84" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q84" s="31">
+        <v>0.22333803165437191</v>
+      </c>
+      <c r="R84" s="31"/>
+      <c r="U84" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="V84" s="32">
+        <v>2.5758605989686227</v>
+      </c>
+      <c r="W84" s="32"/>
+    </row>
+    <row r="85" spans="1:23">
+      <c r="A85" t="s">
+        <v>245</v>
+      </c>
+      <c r="B85" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C85" s="20">
+        <v>233.86496399999999</v>
+      </c>
+      <c r="E85" t="s">
+        <v>106</v>
+      </c>
+      <c r="F85">
+        <v>1.7247182429207868</v>
+      </c>
+      <c r="L85" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="M85" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N85" s="20">
+        <v>240.30364399999999</v>
+      </c>
+      <c r="P85" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q85" s="31">
+        <v>0.41220455814373169</v>
+      </c>
+      <c r="R85" s="31"/>
+    </row>
+    <row r="86" spans="1:23">
+      <c r="A86" t="s">
+        <v>246</v>
+      </c>
+      <c r="B86" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C86" s="20">
+        <v>162.87719300000001</v>
+      </c>
+      <c r="E86" t="s">
+        <v>107</v>
+      </c>
+      <c r="F86">
+        <v>0.31111526997542066</v>
+      </c>
+      <c r="L86" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="M86" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N86" s="20">
+        <v>165.265152</v>
+      </c>
+      <c r="P86" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q86" s="31">
+        <v>1.6838510133356521</v>
+      </c>
+      <c r="R86" s="31"/>
+    </row>
+    <row r="87" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A87" t="s">
+        <v>240</v>
+      </c>
+      <c r="B87" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C87" s="20">
+        <v>190.61299399999999</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F87" s="3">
+        <v>2.0859634472658648</v>
+      </c>
+      <c r="G87" s="3"/>
+      <c r="L87" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="M87" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N87" s="20">
+        <v>194.52795</v>
+      </c>
+      <c r="P87" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q87" s="31">
+        <v>0.82440911628746338</v>
+      </c>
+      <c r="R87" s="31"/>
+    </row>
+    <row r="88" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A88" t="s">
+        <v>242</v>
+      </c>
+      <c r="B88" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C88" s="20">
+        <v>155.07327599999999</v>
+      </c>
+      <c r="L88" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="M88" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N88" s="20">
+        <v>156.904977</v>
+      </c>
+      <c r="P88" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q88" s="32">
+        <v>2.0210753903062737</v>
+      </c>
+      <c r="R88" s="32"/>
+    </row>
+    <row r="89" spans="1:23">
+      <c r="A89" t="s">
+        <v>245</v>
+      </c>
+      <c r="B89" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C89" s="20">
+        <v>190.47191000000001</v>
+      </c>
+      <c r="L89" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="M89" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N89" s="20">
+        <v>166.052301</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23">
+      <c r="A90" t="s">
+        <v>246</v>
+      </c>
+      <c r="B90" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="C90" s="22">
+        <v>201.66666699999999</v>
+      </c>
+      <c r="E90" t="s">
+        <v>174</v>
+      </c>
+      <c r="L90" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="M90" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N90" s="20">
+        <v>235.84090900000001</v>
+      </c>
+      <c r="P90" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A91" s="34"/>
+      <c r="F91" t="s">
+        <v>128</v>
+      </c>
+      <c r="G91" t="s">
+        <v>170</v>
+      </c>
+      <c r="I91" s="34"/>
+      <c r="J91" s="34"/>
+      <c r="K91" s="34"/>
+      <c r="L91" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="M91" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N91" s="20">
+        <v>172.36824300000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23">
+      <c r="A92" s="34"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I92" s="34"/>
+      <c r="J92" s="34"/>
+      <c r="K92" s="34"/>
+      <c r="L92" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="M92" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N92" s="20">
+        <v>156.27201099999999</v>
+      </c>
+      <c r="P92" s="33"/>
+      <c r="Q92" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="R92" s="33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23">
+      <c r="A93" s="36"/>
+      <c r="E93" t="s">
+        <v>99</v>
+      </c>
+      <c r="F93">
+        <v>183.03337318181818</v>
+      </c>
+      <c r="G93">
+        <v>196.14542872727273</v>
+      </c>
+      <c r="I93" s="34"/>
+      <c r="J93" s="34"/>
+      <c r="K93" s="34"/>
+      <c r="L93" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="M93" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N93" s="20">
+        <v>182.36454800000001</v>
+      </c>
+      <c r="P93" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q93" s="31">
+        <v>179.09341186666663</v>
+      </c>
+      <c r="R93" s="31">
+        <v>176.88555675000001</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23">
+      <c r="A94" s="36"/>
+      <c r="E94" t="s">
+        <v>100</v>
+      </c>
+      <c r="F94">
+        <v>906.05921264408391</v>
+      </c>
+      <c r="G94">
+        <v>845.16023000663847</v>
+      </c>
+      <c r="I94" s="35"/>
+      <c r="J94" s="35"/>
+      <c r="K94" s="35"/>
+      <c r="L94" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="M94" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N94" s="20">
+        <v>166.39393899999999</v>
+      </c>
+      <c r="P94" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q94" s="31">
+        <v>1009.9693357996152</v>
+      </c>
+      <c r="R94" s="31">
+        <v>383.39839179197389</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23">
+      <c r="A95" s="36"/>
+      <c r="E95" t="s">
+        <v>101</v>
+      </c>
+      <c r="F95">
+        <v>11</v>
+      </c>
+      <c r="G95">
+        <v>11</v>
+      </c>
+      <c r="I95" s="31"/>
+      <c r="J95" s="31"/>
+      <c r="K95" s="31"/>
+      <c r="L95" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="M95" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N95" s="20">
+        <v>162.85869600000001</v>
+      </c>
+      <c r="P95" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q95" s="31">
+        <v>30</v>
+      </c>
+      <c r="R95" s="31">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23">
+      <c r="A96" s="36"/>
+      <c r="E96" t="s">
+        <v>102</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="I96" s="31"/>
+      <c r="J96" s="31"/>
+      <c r="K96" s="31"/>
+      <c r="L96" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="M96" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N96" s="20">
+        <v>178.34482800000001</v>
+      </c>
+      <c r="P96" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q96" s="31">
+        <v>0</v>
+      </c>
+      <c r="R96" s="31"/>
+    </row>
+    <row r="97" spans="1:18">
+      <c r="A97" s="36"/>
+      <c r="E97" t="s">
+        <v>103</v>
+      </c>
+      <c r="F97">
+        <v>20</v>
+      </c>
+      <c r="I97" s="31"/>
+      <c r="J97" s="31"/>
+      <c r="K97" s="31"/>
+      <c r="L97" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="M97" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="N97" s="22">
+        <v>193.95132699999999</v>
+      </c>
+      <c r="P97" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q97" s="31">
+        <v>33</v>
+      </c>
+      <c r="R97" s="31"/>
+    </row>
+    <row r="98" spans="1:18">
+      <c r="A98" s="36"/>
+      <c r="E98" t="s">
+        <v>104</v>
+      </c>
+      <c r="F98">
+        <v>-1.0391944957649888</v>
+      </c>
+      <c r="I98" s="31"/>
+      <c r="J98" s="31"/>
+      <c r="K98" s="31"/>
+      <c r="L98" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="M98" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N98" s="20">
+        <v>226.71977999999999</v>
+      </c>
+      <c r="P98" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q98" s="31">
+        <v>0.27256325986245744</v>
+      </c>
+      <c r="R98" s="31"/>
+    </row>
+    <row r="99" spans="1:18">
+      <c r="A99" s="36"/>
+      <c r="E99" t="s">
+        <v>105</v>
+      </c>
+      <c r="F99">
+        <v>0.15555763498771033</v>
+      </c>
+      <c r="I99" s="31"/>
+      <c r="J99" s="31"/>
+      <c r="K99" s="31"/>
+      <c r="L99" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="M99" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="N99" s="20">
+        <v>153.97183100000001</v>
+      </c>
+      <c r="P99" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q99" s="31">
+        <v>0.3934436422446595</v>
+      </c>
+      <c r="R99" s="31"/>
+    </row>
+    <row r="100" spans="1:18">
+      <c r="A100" s="36"/>
+      <c r="E100" t="s">
+        <v>106</v>
+      </c>
+      <c r="F100">
+        <v>1.7247182429207868</v>
+      </c>
+      <c r="I100" s="31"/>
+      <c r="J100" s="31"/>
+      <c r="K100" s="31"/>
+      <c r="L100" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="M100" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="N100" s="20">
+        <v>149.02941200000001</v>
+      </c>
+      <c r="P100" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q100" s="31">
+        <v>1.6923603090303456</v>
+      </c>
+      <c r="R100" s="31"/>
+    </row>
+    <row r="101" spans="1:18">
+      <c r="A101" s="36"/>
+      <c r="E101" t="s">
+        <v>107</v>
+      </c>
+      <c r="F101">
+        <v>0.31111526997542066</v>
+      </c>
+      <c r="I101" s="31"/>
+      <c r="J101" s="31"/>
+      <c r="K101" s="31"/>
+      <c r="L101" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="M101" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="N101" s="20">
+        <v>179.045455</v>
+      </c>
+      <c r="P101" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q101" s="31">
+        <v>0.78688728448931899</v>
+      </c>
+      <c r="R101" s="31"/>
+    </row>
+    <row r="102" spans="1:18" ht="15.75" thickBot="1">
+      <c r="A102" s="36"/>
+      <c r="E102" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F102" s="3">
+        <v>2.0859634472658648</v>
+      </c>
+      <c r="G102" s="3"/>
+      <c r="I102" s="31"/>
+      <c r="J102" s="31"/>
+      <c r="K102" s="31"/>
+      <c r="L102" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="M102" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="N102" s="20">
+        <v>190.340136</v>
+      </c>
+      <c r="P102" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q102" s="32">
+        <v>2.0345152974493397</v>
+      </c>
+      <c r="R102" s="32"/>
+    </row>
+    <row r="103" spans="1:18">
+      <c r="A103" s="36"/>
+      <c r="I103" s="31"/>
+      <c r="J103" s="31"/>
+      <c r="K103" s="31"/>
+      <c r="L103" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="M103" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="N103" s="20">
+        <v>153.51952</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18">
+      <c r="A104" s="36"/>
+      <c r="I104" s="31"/>
+      <c r="J104" s="31"/>
+      <c r="K104" s="31"/>
+      <c r="L104" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="M104" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="N104" s="20">
+        <v>171.88356200000001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18">
+      <c r="A105" s="36"/>
+      <c r="I105" s="34"/>
+      <c r="J105" s="34"/>
+      <c r="K105" s="34"/>
+      <c r="L105" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="M105" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="N105" s="20">
+        <v>174.05384599999999</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18">
+      <c r="A106" s="36"/>
+      <c r="I106" s="34"/>
+      <c r="J106" s="34"/>
+      <c r="K106" s="34"/>
+      <c r="L106" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="M106" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="N106" s="20">
+        <v>176.79674800000001</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18">
+      <c r="A107" s="36"/>
+      <c r="I107" s="34"/>
+      <c r="J107" s="34"/>
+      <c r="K107" s="34"/>
+      <c r="L107" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="M107" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="N107" s="20">
+        <v>181.13793100000001</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18">
+      <c r="A108" s="36"/>
+      <c r="L108" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="M108" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="N108" s="20">
+        <v>168.39919399999999</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18">
+      <c r="A109" s="36"/>
+      <c r="L109" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="M109" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="N109" s="20">
+        <v>173.75877199999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18">
+      <c r="A110" s="36"/>
+      <c r="L110" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="M110" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="N110" s="20">
+        <v>227.647887</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18">
+      <c r="A111" s="36"/>
+      <c r="L111" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="M111" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="N111" s="20">
+        <v>177.014218</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18">
+      <c r="A112" s="36"/>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="36"/>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="36"/>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="34"/>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="34"/>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="34"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <tableParts count="2">
-    <tablePart r:id="rId3"/>
-    <tablePart r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <drawing r:id="rId4"/>
+  <tableParts count="6">
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08CBB891-F584-4F5A-A553-41469C7D6F94}">
-  <dimension ref="C1:AO167"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="B1:AO196"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="57.1796875" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="57.140625" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="9" max="9" width="58.26953125" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="58.28515625" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="15" width="11.81640625" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:16">
+    <row r="1" spans="2:16">
+      <c r="B1" t="s">
+        <v>273</v>
+      </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
@@ -18128,6 +22189,9 @@
       <c r="F1" t="s">
         <v>95</v>
       </c>
+      <c r="H1" t="s">
+        <v>235</v>
+      </c>
       <c r="I1" t="s">
         <v>0</v>
       </c>
@@ -18153,7 +22217,10 @@
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="3:16">
+    <row r="2" spans="2:16">
+      <c r="B2" s="19" t="s">
+        <v>236</v>
+      </c>
       <c r="C2" s="2" t="s">
         <v>65</v>
       </c>
@@ -18167,6 +22234,9 @@
         <f>AVERAGE(Table1[[#This Row],[P1]]:Table1[[#This Row],[P2]])</f>
         <v>16.704914500000001</v>
       </c>
+      <c r="H2" t="s">
+        <v>247</v>
+      </c>
       <c r="I2" s="2" t="s">
         <v>66</v>
       </c>
@@ -18196,7 +22266,10 @@
         <v>25.371325666666667</v>
       </c>
     </row>
-    <row r="3" spans="3:16">
+    <row r="3" spans="2:16">
+      <c r="B3" s="19" t="s">
+        <v>237</v>
+      </c>
       <c r="C3" s="2" t="s">
         <v>64</v>
       </c>
@@ -18210,6 +22283,9 @@
         <f>AVERAGE(Table1[[#This Row],[P1]]:Table1[[#This Row],[P2]])</f>
         <v>32.124985500000001</v>
       </c>
+      <c r="H3" t="s">
+        <v>249</v>
+      </c>
       <c r="I3" s="2" t="s">
         <v>68</v>
       </c>
@@ -18239,7 +22315,10 @@
         <v>20.852425</v>
       </c>
     </row>
-    <row r="4" spans="3:16">
+    <row r="4" spans="2:16">
+      <c r="B4" s="19" t="s">
+        <v>238</v>
+      </c>
       <c r="C4" s="2" t="s">
         <v>62</v>
       </c>
@@ -18253,6 +22332,9 @@
         <f>AVERAGE(Table1[[#This Row],[P1]]:Table1[[#This Row],[P2]])</f>
         <v>33.195755500000004</v>
       </c>
+      <c r="H4" t="s">
+        <v>250</v>
+      </c>
       <c r="I4" s="2" t="s">
         <v>69</v>
       </c>
@@ -18282,7 +22364,10 @@
         <v>12.094702666666668</v>
       </c>
     </row>
-    <row r="5" spans="3:16">
+    <row r="5" spans="2:16">
+      <c r="B5" s="19" t="s">
+        <v>239</v>
+      </c>
       <c r="C5" s="2" t="s">
         <v>61</v>
       </c>
@@ -18296,6 +22381,9 @@
         <f>AVERAGE(Table1[[#This Row],[P1]]:Table1[[#This Row],[P2]])</f>
         <v>38.681583500000002</v>
       </c>
+      <c r="H5" t="s">
+        <v>251</v>
+      </c>
       <c r="I5" s="2" t="s">
         <v>70</v>
       </c>
@@ -18325,7 +22413,10 @@
         <v>30.031203000000001</v>
       </c>
     </row>
-    <row r="6" spans="3:16">
+    <row r="6" spans="2:16">
+      <c r="B6" s="19" t="s">
+        <v>240</v>
+      </c>
       <c r="C6" s="2" t="s">
         <v>59</v>
       </c>
@@ -18339,6 +22430,9 @@
         <f>AVERAGE(Table1[[#This Row],[P1]]:Table1[[#This Row],[P2]])</f>
         <v>24.0545115</v>
       </c>
+      <c r="H6" t="s">
+        <v>252</v>
+      </c>
       <c r="I6" s="2" t="s">
         <v>71</v>
       </c>
@@ -18368,7 +22462,10 @@
         <v>15.313345666666665</v>
       </c>
     </row>
-    <row r="7" spans="3:16">
+    <row r="7" spans="2:16">
+      <c r="B7" s="19" t="s">
+        <v>241</v>
+      </c>
       <c r="C7" s="2" t="s">
         <v>58</v>
       </c>
@@ -18382,6 +22479,9 @@
         <f>AVERAGE(Table1[[#This Row],[P1]]:Table1[[#This Row],[P2]])</f>
         <v>26.1464055</v>
       </c>
+      <c r="H7" t="s">
+        <v>253</v>
+      </c>
       <c r="I7" s="2" t="s">
         <v>73</v>
       </c>
@@ -18411,7 +22511,10 @@
         <v>8.8733186666666661</v>
       </c>
     </row>
-    <row r="8" spans="3:16">
+    <row r="8" spans="2:16">
+      <c r="B8" s="19" t="s">
+        <v>242</v>
+      </c>
       <c r="C8" s="2" t="s">
         <v>57</v>
       </c>
@@ -18425,6 +22528,9 @@
         <f>AVERAGE(Table1[[#This Row],[P1]]:Table1[[#This Row],[P2]])</f>
         <v>31.984910499999998</v>
       </c>
+      <c r="H8" t="s">
+        <v>254</v>
+      </c>
       <c r="I8" s="2" t="s">
         <v>74</v>
       </c>
@@ -18454,7 +22560,10 @@
         <v>13.473684333333333</v>
       </c>
     </row>
-    <row r="9" spans="3:16">
+    <row r="9" spans="2:16">
+      <c r="B9" s="19" t="s">
+        <v>243</v>
+      </c>
       <c r="C9" s="2" t="s">
         <v>56</v>
       </c>
@@ -18468,6 +22577,9 @@
         <f>AVERAGE(Table1[[#This Row],[P1]]:Table1[[#This Row],[P2]])</f>
         <v>42.809500999999997</v>
       </c>
+      <c r="H9" t="s">
+        <v>255</v>
+      </c>
       <c r="I9" s="2" t="s">
         <v>75</v>
       </c>
@@ -18497,7 +22609,10 @@
         <v>24.944554999999998</v>
       </c>
     </row>
-    <row r="10" spans="3:16">
+    <row r="10" spans="2:16">
+      <c r="B10" s="19" t="s">
+        <v>244</v>
+      </c>
       <c r="C10" s="2" t="s">
         <v>55</v>
       </c>
@@ -18511,6 +22626,9 @@
         <f>AVERAGE(Table1[[#This Row],[P1]]:Table1[[#This Row],[P2]])</f>
         <v>14.999921000000001</v>
       </c>
+      <c r="H10" t="s">
+        <v>248</v>
+      </c>
       <c r="I10" s="2" t="s">
         <v>49</v>
       </c>
@@ -18540,7 +22658,10 @@
         <v>19.701947333333333</v>
       </c>
     </row>
-    <row r="11" spans="3:16">
+    <row r="11" spans="2:16">
+      <c r="B11" s="19" t="s">
+        <v>245</v>
+      </c>
       <c r="C11" s="2" t="s">
         <v>54</v>
       </c>
@@ -18554,6 +22675,9 @@
         <f>AVERAGE(Table1[[#This Row],[P1]]:Table1[[#This Row],[P2]])</f>
         <v>23.851616499999999</v>
       </c>
+      <c r="H11" t="s">
+        <v>257</v>
+      </c>
       <c r="I11" s="2" t="s">
         <v>154</v>
       </c>
@@ -18583,7 +22707,10 @@
         <v>24.356252999999999</v>
       </c>
     </row>
-    <row r="12" spans="3:16">
+    <row r="12" spans="2:16">
+      <c r="B12" s="21" t="s">
+        <v>246</v>
+      </c>
       <c r="C12" s="2" t="s">
         <v>157</v>
       </c>
@@ -18597,6 +22724,9 @@
         <f>AVERAGE(Table1[[#This Row],[P1]]:Table1[[#This Row],[P2]])</f>
         <v>26.732667999999997</v>
       </c>
+      <c r="H12" t="s">
+        <v>256</v>
+      </c>
       <c r="I12" s="2" t="s">
         <v>155</v>
       </c>
@@ -18626,9 +22756,12 @@
         <v>18.110859999999999</v>
       </c>
     </row>
-    <row r="13" spans="3:16">
+    <row r="13" spans="2:16">
       <c r="D13" t="s">
         <v>91</v>
+      </c>
+      <c r="H13" t="s">
+        <v>260</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>156</v>
@@ -18659,11 +22792,14 @@
         <v>19.365356999999999</v>
       </c>
     </row>
-    <row r="14" spans="3:16">
+    <row r="14" spans="2:16">
       <c r="D14">
         <f>CORREL(Table1[P1],Table1[P2])</f>
         <v>-9.2422075988005239E-2</v>
       </c>
+      <c r="H14" t="s">
+        <v>258</v>
+      </c>
       <c r="I14" s="2" t="s">
         <v>158</v>
       </c>
@@ -18693,7 +22829,10 @@
         <v>21.717865666666668</v>
       </c>
     </row>
-    <row r="15" spans="3:16">
+    <row r="15" spans="2:16">
+      <c r="H15" t="s">
+        <v>259</v>
+      </c>
       <c r="I15" s="2" t="s">
         <v>159</v>
       </c>
@@ -18749,7 +22888,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="48" spans="4:23" ht="15" thickBot="1">
+    <row r="48" spans="4:23" ht="15.75" thickBot="1">
       <c r="D48">
         <v>2.4711409999999998</v>
       </c>
@@ -18917,7 +23056,7 @@
       <c r="V59" s="9"/>
       <c r="W59" s="9"/>
     </row>
-    <row r="60" spans="4:23" ht="15" thickBot="1">
+    <row r="60" spans="4:23" ht="15.75" thickBot="1">
       <c r="K60" s="3" t="s">
         <v>108</v>
       </c>
@@ -19043,7 +23182,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="77" spans="4:6" ht="15" thickBot="1"/>
+    <row r="77" spans="4:6" ht="15.75" thickBot="1"/>
     <row r="78" spans="4:6">
       <c r="D78" s="8" t="s">
         <v>116</v>
@@ -19085,7 +23224,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="83" spans="4:17" ht="15" thickBot="1">
+    <row r="83" spans="4:17" ht="15.75" thickBot="1">
       <c r="D83" s="3" t="s">
         <v>101</v>
       </c>
@@ -19102,7 +23241,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="85" spans="4:17" ht="15" thickBot="1">
+    <row r="85" spans="4:17" ht="15.75" thickBot="1">
       <c r="D85" t="s">
         <v>121</v>
       </c>
@@ -19195,7 +23334,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="4:17" ht="15" thickBot="1">
+    <row r="89" spans="4:17" ht="15.75" thickBot="1">
       <c r="D89" s="3" t="s">
         <v>124</v>
       </c>
@@ -19215,7 +23354,7 @@
         <v>2.1493368459329587</v>
       </c>
     </row>
-    <row r="90" spans="4:17" ht="15" thickBot="1">
+    <row r="90" spans="4:17" ht="15.75" thickBot="1">
       <c r="O90" t="s">
         <v>161</v>
       </c>
@@ -19223,7 +23362,7 @@
         <v>9.843683670970256E-2</v>
       </c>
     </row>
-    <row r="91" spans="4:17" ht="15" thickBot="1">
+    <row r="91" spans="4:17" ht="15.75" thickBot="1">
       <c r="D91" s="4"/>
       <c r="E91" s="4" t="s">
         <v>130</v>
@@ -19286,7 +23425,7 @@
         <v>37.855258279391578</v>
       </c>
     </row>
-    <row r="93" spans="4:17" ht="15" thickBot="1">
+    <row r="93" spans="4:17" ht="15.75" thickBot="1">
       <c r="D93" s="3" t="s">
         <v>136</v>
       </c>
@@ -19320,7 +23459,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="98" spans="4:35" ht="15" thickBot="1"/>
+    <row r="98" spans="4:35" ht="15.75" thickBot="1"/>
     <row r="99" spans="4:35">
       <c r="D99" s="8" t="s">
         <v>116</v>
@@ -19359,7 +23498,7 @@
         <v>10.910273656348574</v>
       </c>
     </row>
-    <row r="104" spans="4:35" ht="15" thickBot="1">
+    <row r="104" spans="4:35" ht="15.75" thickBot="1">
       <c r="D104" s="3" t="s">
         <v>101</v>
       </c>
@@ -19367,7 +23506,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="4:35" ht="15" thickBot="1">
+    <row r="106" spans="4:35" ht="15.75" thickBot="1">
       <c r="D106" t="s">
         <v>121</v>
       </c>
@@ -19424,7 +23563,7 @@
         <v>119.03407125641368</v>
       </c>
     </row>
-    <row r="110" spans="4:35" ht="15" thickBot="1">
+    <row r="110" spans="4:35" ht="15.75" thickBot="1">
       <c r="D110" s="3" t="s">
         <v>124</v>
       </c>
@@ -19444,7 +23583,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="111" spans="4:35" ht="15" thickBot="1"/>
+    <row r="111" spans="4:35" ht="15.75" thickBot="1"/>
     <row r="112" spans="4:35">
       <c r="D112" s="4"/>
       <c r="E112" s="4" t="s">
@@ -19511,7 +23650,7 @@
         <v>0.55522926444419129</v>
       </c>
     </row>
-    <row r="114" spans="4:41" ht="15" thickBot="1">
+    <row r="114" spans="4:41" ht="15.75" thickBot="1">
       <c r="D114" s="3" t="s">
         <v>136</v>
       </c>
@@ -19562,7 +23701,7 @@
         <v>4.505428874124374</v>
       </c>
     </row>
-    <row r="117" spans="4:41" ht="15" thickBot="1">
+    <row r="117" spans="4:41" ht="15.75" thickBot="1">
       <c r="AG117" s="3" t="s">
         <v>101</v>
       </c>
@@ -19570,7 +23709,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="119" spans="4:41" ht="15" thickBot="1">
+    <row r="119" spans="4:41" ht="15.75" thickBot="1">
       <c r="T119" s="6" t="s">
         <v>88</v>
       </c>
@@ -19663,7 +23802,7 @@
         <v>20.298889339793625</v>
       </c>
     </row>
-    <row r="123" spans="4:41" ht="15" thickBot="1">
+    <row r="123" spans="4:41" ht="15.75" thickBot="1">
       <c r="T123">
         <v>7.7812380000000001</v>
       </c>
@@ -19686,7 +23825,7 @@
       <c r="AK123" s="3"/>
       <c r="AL123" s="3"/>
     </row>
-    <row r="124" spans="4:41" ht="15" thickBot="1">
+    <row r="124" spans="4:41" ht="15.75" thickBot="1">
       <c r="T124">
         <v>8.8605520000000002</v>
       </c>
@@ -19771,7 +23910,7 @@
         <v>11.99073981527739</v>
       </c>
     </row>
-    <row r="127" spans="4:41" ht="15" thickBot="1">
+    <row r="127" spans="4:41" ht="15.75" thickBot="1">
       <c r="T127">
         <v>13.606121</v>
       </c>
@@ -19821,7 +23960,7 @@
         <v>31.080375</v>
       </c>
     </row>
-    <row r="129" spans="20:38">
+    <row r="129" spans="2:38">
       <c r="T129">
         <v>19.296327000000002</v>
       </c>
@@ -19832,7 +23971,7 @@
         <v>32.160544999999999</v>
       </c>
     </row>
-    <row r="130" spans="20:38">
+    <row r="130" spans="2:38">
       <c r="T130">
         <v>15.797788000000001</v>
       </c>
@@ -19846,7 +23985,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="131" spans="20:38" ht="15" thickBot="1">
+    <row r="131" spans="2:38" ht="15.75" thickBot="1">
       <c r="T131">
         <v>14.677982999999999</v>
       </c>
@@ -19857,7 +23996,7 @@
         <v>21.965651999999999</v>
       </c>
     </row>
-    <row r="132" spans="20:38">
+    <row r="132" spans="2:38">
       <c r="T132">
         <v>17.541353000000001</v>
       </c>
@@ -19872,7 +24011,10 @@
       </c>
       <c r="AH132" s="8"/>
     </row>
-    <row r="133" spans="20:38">
+    <row r="133" spans="2:38">
+      <c r="B133" s="23" t="s">
+        <v>261</v>
+      </c>
       <c r="T133">
         <v>19.592489</v>
       </c>
@@ -19889,7 +24031,7 @@
         <v>0.12237744065125283</v>
       </c>
     </row>
-    <row r="134" spans="20:38">
+    <row r="134" spans="2:38">
       <c r="AG134" t="s">
         <v>118</v>
       </c>
@@ -19897,7 +24039,49 @@
         <v>1.4976237980350908E-2</v>
       </c>
     </row>
-    <row r="135" spans="20:38">
+    <row r="135" spans="2:38">
+      <c r="B135" t="s">
+        <v>273</v>
+      </c>
+      <c r="C135" t="s">
+        <v>0</v>
+      </c>
+      <c r="D135" t="s">
+        <v>262</v>
+      </c>
+      <c r="E135" t="s">
+        <v>88</v>
+      </c>
+      <c r="F135" t="s">
+        <v>263</v>
+      </c>
+      <c r="G135" t="s">
+        <v>89</v>
+      </c>
+      <c r="K135" t="s">
+        <v>235</v>
+      </c>
+      <c r="L135" t="s">
+        <v>0</v>
+      </c>
+      <c r="M135" t="s">
+        <v>262</v>
+      </c>
+      <c r="N135" t="s">
+        <v>88</v>
+      </c>
+      <c r="O135" t="s">
+        <v>263</v>
+      </c>
+      <c r="P135" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>264</v>
+      </c>
+      <c r="R135" t="s">
+        <v>90</v>
+      </c>
       <c r="AG135" t="s">
         <v>119</v>
       </c>
@@ -19905,7 +24089,49 @@
         <v>-6.7109075521286518E-2</v>
       </c>
     </row>
-    <row r="136" spans="20:38">
+    <row r="136" spans="2:38">
+      <c r="B136" t="s">
+        <v>236</v>
+      </c>
+      <c r="C136" t="s">
+        <v>65</v>
+      </c>
+      <c r="D136" t="s">
+        <v>128</v>
+      </c>
+      <c r="E136">
+        <v>2.4711409999999998</v>
+      </c>
+      <c r="F136" t="s">
+        <v>128</v>
+      </c>
+      <c r="G136">
+        <v>30.938687999999999</v>
+      </c>
+      <c r="K136" t="s">
+        <v>247</v>
+      </c>
+      <c r="L136" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M136" t="s">
+        <v>128</v>
+      </c>
+      <c r="N136" s="2">
+        <v>13.27946</v>
+      </c>
+      <c r="O136" t="s">
+        <v>170</v>
+      </c>
+      <c r="P136" s="2">
+        <v>26.720863999999999</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>128</v>
+      </c>
+      <c r="R136" s="2">
+        <v>36.113652999999999</v>
+      </c>
       <c r="AG136" t="s">
         <v>120</v>
       </c>
@@ -19913,7 +24139,49 @@
         <v>5.3764322758177139</v>
       </c>
     </row>
-    <row r="137" spans="20:38" ht="15" thickBot="1">
+    <row r="137" spans="2:38" ht="15.75" thickBot="1">
+      <c r="B137" t="s">
+        <v>237</v>
+      </c>
+      <c r="C137" t="s">
+        <v>64</v>
+      </c>
+      <c r="D137" t="s">
+        <v>170</v>
+      </c>
+      <c r="E137">
+        <v>32.792991000000001</v>
+      </c>
+      <c r="F137" t="s">
+        <v>128</v>
+      </c>
+      <c r="G137">
+        <v>31.456980000000001</v>
+      </c>
+      <c r="K137" t="s">
+        <v>249</v>
+      </c>
+      <c r="L137" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M137" t="s">
+        <v>128</v>
+      </c>
+      <c r="N137" s="2">
+        <v>18.098331000000002</v>
+      </c>
+      <c r="O137" t="s">
+        <v>128</v>
+      </c>
+      <c r="P137" s="2">
+        <v>29.803229999999999</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>128</v>
+      </c>
+      <c r="R137" s="2">
+        <v>14.655714</v>
+      </c>
       <c r="AG137" s="3" t="s">
         <v>101</v>
       </c>
@@ -19921,12 +24189,140 @@
         <v>14</v>
       </c>
     </row>
-    <row r="139" spans="20:38" ht="15" thickBot="1">
+    <row r="138" spans="2:38">
+      <c r="B138" t="s">
+        <v>238</v>
+      </c>
+      <c r="C138" t="s">
+        <v>62</v>
+      </c>
+      <c r="D138" t="s">
+        <v>128</v>
+      </c>
+      <c r="E138">
+        <v>32.033904</v>
+      </c>
+      <c r="F138" t="s">
+        <v>128</v>
+      </c>
+      <c r="G138">
+        <v>34.357607000000002</v>
+      </c>
+      <c r="K138" t="s">
+        <v>250</v>
+      </c>
+      <c r="L138" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M138" t="s">
+        <v>128</v>
+      </c>
+      <c r="N138" s="7">
+        <v>2.2134100000000001</v>
+      </c>
+      <c r="O138" t="s">
+        <v>170</v>
+      </c>
+      <c r="P138" s="2">
+        <v>11.462300000000001</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>128</v>
+      </c>
+      <c r="R138" s="2">
+        <v>22.608398000000001</v>
+      </c>
+    </row>
+    <row r="139" spans="2:38" ht="15.75" thickBot="1">
+      <c r="B139" t="s">
+        <v>239</v>
+      </c>
+      <c r="C139" t="s">
+        <v>61</v>
+      </c>
+      <c r="D139" t="s">
+        <v>128</v>
+      </c>
+      <c r="E139">
+        <v>38.272494999999999</v>
+      </c>
+      <c r="F139" t="s">
+        <v>128</v>
+      </c>
+      <c r="G139">
+        <v>39.090671999999998</v>
+      </c>
+      <c r="K139" t="s">
+        <v>251</v>
+      </c>
+      <c r="L139" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M139" t="s">
+        <v>128</v>
+      </c>
+      <c r="N139" s="2">
+        <v>24.187462</v>
+      </c>
+      <c r="O139" t="s">
+        <v>128</v>
+      </c>
+      <c r="P139" s="2">
+        <v>7.7812380000000001</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>128</v>
+      </c>
+      <c r="R139" s="7">
+        <v>58.124909000000002</v>
+      </c>
       <c r="AG139" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="140" spans="20:38">
+    <row r="140" spans="2:38">
+      <c r="B140" t="s">
+        <v>240</v>
+      </c>
+      <c r="C140" t="s">
+        <v>59</v>
+      </c>
+      <c r="D140" t="s">
+        <v>170</v>
+      </c>
+      <c r="E140">
+        <v>17.652170000000002</v>
+      </c>
+      <c r="F140" t="s">
+        <v>170</v>
+      </c>
+      <c r="G140">
+        <v>30.456852999999999</v>
+      </c>
+      <c r="K140" t="s">
+        <v>252</v>
+      </c>
+      <c r="L140" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M140" t="s">
+        <v>128</v>
+      </c>
+      <c r="N140" s="2">
+        <v>13.098208</v>
+      </c>
+      <c r="O140" t="s">
+        <v>128</v>
+      </c>
+      <c r="P140" s="2">
+        <v>8.8605520000000002</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>128</v>
+      </c>
+      <c r="R140" s="2">
+        <v>23.981276999999999</v>
+      </c>
       <c r="AG140" s="4"/>
       <c r="AH140" s="4" t="s">
         <v>103</v>
@@ -19944,7 +24340,49 @@
         <v>129</v>
       </c>
     </row>
-    <row r="141" spans="20:38">
+    <row r="141" spans="2:38">
+      <c r="B141" t="s">
+        <v>241</v>
+      </c>
+      <c r="C141" t="s">
+        <v>58</v>
+      </c>
+      <c r="D141" t="s">
+        <v>170</v>
+      </c>
+      <c r="E141">
+        <v>13.541086</v>
+      </c>
+      <c r="F141" t="s">
+        <v>128</v>
+      </c>
+      <c r="G141">
+        <v>38.751725</v>
+      </c>
+      <c r="K141" t="s">
+        <v>253</v>
+      </c>
+      <c r="L141" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M141" t="s">
+        <v>128</v>
+      </c>
+      <c r="N141" s="2">
+        <v>9.9307610000000004</v>
+      </c>
+      <c r="O141" t="s">
+        <v>128</v>
+      </c>
+      <c r="P141" s="2">
+        <v>10.206614999999999</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>128</v>
+      </c>
+      <c r="R141" s="2">
+        <v>6.4825799999999996</v>
+      </c>
       <c r="AG141" t="s">
         <v>122</v>
       </c>
@@ -19964,7 +24402,49 @@
         <v>0.67684228954421721</v>
       </c>
     </row>
-    <row r="142" spans="20:38">
+    <row r="142" spans="2:38">
+      <c r="B142" t="s">
+        <v>242</v>
+      </c>
+      <c r="C142" t="s">
+        <v>57</v>
+      </c>
+      <c r="D142" t="s">
+        <v>170</v>
+      </c>
+      <c r="E142">
+        <v>22.615593000000001</v>
+      </c>
+      <c r="F142" t="s">
+        <v>170</v>
+      </c>
+      <c r="G142">
+        <v>41.354227999999999</v>
+      </c>
+      <c r="K142" t="s">
+        <v>254</v>
+      </c>
+      <c r="L142" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="M142" t="s">
+        <v>128</v>
+      </c>
+      <c r="N142" s="2">
+        <v>18.789473999999998</v>
+      </c>
+      <c r="O142" t="s">
+        <v>170</v>
+      </c>
+      <c r="P142" s="2">
+        <v>14.210526</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>128</v>
+      </c>
+      <c r="R142" s="2">
+        <v>7.4210529999999997</v>
+      </c>
       <c r="AG142" t="s">
         <v>123</v>
       </c>
@@ -19978,7 +24458,49 @@
         <v>28.906024016454442</v>
       </c>
     </row>
-    <row r="143" spans="20:38" ht="15" thickBot="1">
+    <row r="143" spans="2:38" ht="15.75" thickBot="1">
+      <c r="B143" t="s">
+        <v>243</v>
+      </c>
+      <c r="C143" t="s">
+        <v>56</v>
+      </c>
+      <c r="D143" t="s">
+        <v>170</v>
+      </c>
+      <c r="E143">
+        <v>60.294035000000001</v>
+      </c>
+      <c r="F143" t="s">
+        <v>128</v>
+      </c>
+      <c r="G143">
+        <v>25.324967000000001</v>
+      </c>
+      <c r="K143" t="s">
+        <v>255</v>
+      </c>
+      <c r="L143" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M143" t="s">
+        <v>128</v>
+      </c>
+      <c r="N143" s="2">
+        <v>13.606121</v>
+      </c>
+      <c r="O143" t="s">
+        <v>128</v>
+      </c>
+      <c r="P143" s="2">
+        <v>26.940118999999999</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>128</v>
+      </c>
+      <c r="R143" s="2">
+        <v>34.287424999999999</v>
+      </c>
       <c r="AG143" s="3" t="s">
         <v>124</v>
       </c>
@@ -19992,8 +24514,93 @@
       <c r="AK143" s="3"/>
       <c r="AL143" s="3"/>
     </row>
-    <row r="144" spans="20:38" ht="15" thickBot="1"/>
-    <row r="145" spans="33:41">
+    <row r="144" spans="2:38" ht="15.75" thickBot="1">
+      <c r="B144" t="s">
+        <v>244</v>
+      </c>
+      <c r="C144" t="s">
+        <v>55</v>
+      </c>
+      <c r="D144" t="s">
+        <v>128</v>
+      </c>
+      <c r="E144">
+        <v>5.3683930000000002</v>
+      </c>
+      <c r="F144" t="s">
+        <v>128</v>
+      </c>
+      <c r="G144">
+        <v>24.631449</v>
+      </c>
+      <c r="K144" t="s">
+        <v>248</v>
+      </c>
+      <c r="L144" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M144" t="s">
+        <v>128</v>
+      </c>
+      <c r="N144" s="2">
+        <v>31.080375</v>
+      </c>
+      <c r="O144" t="s">
+        <v>170</v>
+      </c>
+      <c r="P144" s="2">
+        <v>10.094481</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>128</v>
+      </c>
+      <c r="R144" s="2">
+        <v>17.930986000000001</v>
+      </c>
+    </row>
+    <row r="145" spans="2:41">
+      <c r="B145" t="s">
+        <v>245</v>
+      </c>
+      <c r="C145" t="s">
+        <v>54</v>
+      </c>
+      <c r="D145" t="s">
+        <v>170</v>
+      </c>
+      <c r="E145">
+        <v>27.407136999999999</v>
+      </c>
+      <c r="F145" t="s">
+        <v>170</v>
+      </c>
+      <c r="G145">
+        <v>20.296095999999999</v>
+      </c>
+      <c r="K145" t="s">
+        <v>257</v>
+      </c>
+      <c r="L145" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="M145" t="s">
+        <v>170</v>
+      </c>
+      <c r="N145" s="2">
+        <v>32.160544999999999</v>
+      </c>
+      <c r="O145" t="s">
+        <v>128</v>
+      </c>
+      <c r="P145" s="2">
+        <v>19.296327000000002</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>128</v>
+      </c>
+      <c r="R145" s="2">
+        <v>21.611886999999999</v>
+      </c>
       <c r="AG145" s="4"/>
       <c r="AH145" s="4" t="s">
         <v>130</v>
@@ -20020,7 +24627,49 @@
         <v>135</v>
       </c>
     </row>
-    <row r="146" spans="33:41">
+    <row r="146" spans="2:41">
+      <c r="B146" t="s">
+        <v>246</v>
+      </c>
+      <c r="C146" t="s">
+        <v>157</v>
+      </c>
+      <c r="D146" t="s">
+        <v>170</v>
+      </c>
+      <c r="E146">
+        <v>18.118190999999999</v>
+      </c>
+      <c r="F146" t="s">
+        <v>170</v>
+      </c>
+      <c r="G146">
+        <v>35.347144999999998</v>
+      </c>
+      <c r="K146" t="s">
+        <v>256</v>
+      </c>
+      <c r="L146" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="M146" t="s">
+        <v>170</v>
+      </c>
+      <c r="N146" s="2">
+        <v>15.797788000000001</v>
+      </c>
+      <c r="O146" t="s">
+        <v>170</v>
+      </c>
+      <c r="P146" s="2">
+        <v>20.227074999999999</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>128</v>
+      </c>
+      <c r="R146" s="2">
+        <v>18.307717</v>
+      </c>
       <c r="AG146" t="s">
         <v>125</v>
       </c>
@@ -20049,7 +24698,31 @@
         <v>19.508322334293815</v>
       </c>
     </row>
-    <row r="147" spans="33:41" ht="15" thickBot="1">
+    <row r="147" spans="2:41" ht="15.75" thickBot="1">
+      <c r="K147" t="s">
+        <v>260</v>
+      </c>
+      <c r="L147" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="M147" t="s">
+        <v>128</v>
+      </c>
+      <c r="N147" s="2">
+        <v>21.965651999999999</v>
+      </c>
+      <c r="O147" t="s">
+        <v>128</v>
+      </c>
+      <c r="P147" s="2">
+        <v>14.677982999999999</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>170</v>
+      </c>
+      <c r="R147" s="2">
+        <v>21.452435999999999</v>
+      </c>
       <c r="AG147" s="3" t="s">
         <v>136</v>
       </c>
@@ -20078,19 +24751,132 @@
         <v>0.35181955680699473</v>
       </c>
     </row>
-    <row r="150" spans="33:41">
+    <row r="148" spans="2:41">
+      <c r="K148" t="s">
+        <v>258</v>
+      </c>
+      <c r="L148" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="M148" t="s">
+        <v>170</v>
+      </c>
+      <c r="N148" s="2">
+        <v>18.728362000000001</v>
+      </c>
+      <c r="O148" t="s">
+        <v>170</v>
+      </c>
+      <c r="P148" s="2">
+        <v>28.883882</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>170</v>
+      </c>
+      <c r="R148" s="2">
+        <v>17.541353000000001</v>
+      </c>
+    </row>
+    <row r="149" spans="2:41">
+      <c r="K149" t="s">
+        <v>259</v>
+      </c>
+      <c r="L149" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="M149" t="s">
+        <v>128</v>
+      </c>
+      <c r="N149" s="2">
+        <v>28.657671000000001</v>
+      </c>
+      <c r="O149" t="s">
+        <v>128</v>
+      </c>
+      <c r="P149" s="2">
+        <v>20.567240000000002</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>170</v>
+      </c>
+      <c r="R149" s="2">
+        <v>19.592489</v>
+      </c>
+    </row>
+    <row r="150" spans="2:41">
+      <c r="B150" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="C150" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="D150" t="s">
+        <v>274</v>
+      </c>
+      <c r="F150" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="G150" t="s">
+        <v>275</v>
+      </c>
       <c r="AG150" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="151" spans="33:41" ht="15" thickBot="1"/>
-    <row r="152" spans="33:41">
+    <row r="151" spans="2:41" ht="15.75" thickBot="1">
+      <c r="B151" t="s">
+        <v>236</v>
+      </c>
+      <c r="C151" t="s">
+        <v>128</v>
+      </c>
+      <c r="D151">
+        <v>2.4711409999999998</v>
+      </c>
+      <c r="F151" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="G151" s="37">
+        <v>27.518001909090909</v>
+      </c>
+    </row>
+    <row r="152" spans="2:41">
+      <c r="B152" t="s">
+        <v>238</v>
+      </c>
+      <c r="C152" t="s">
+        <v>128</v>
+      </c>
+      <c r="D152">
+        <v>32.033904</v>
+      </c>
+      <c r="F152" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="G152" s="37">
+        <v>29.079593181818179</v>
+      </c>
       <c r="AG152" s="8" t="s">
         <v>116</v>
       </c>
       <c r="AH152" s="8"/>
     </row>
-    <row r="153" spans="33:41">
+    <row r="153" spans="2:41">
+      <c r="B153" t="s">
+        <v>239</v>
+      </c>
+      <c r="C153" t="s">
+        <v>128</v>
+      </c>
+      <c r="D153">
+        <v>38.272494999999999</v>
+      </c>
+      <c r="F153" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="G153" s="37">
+        <v>28.298797545454544</v>
+      </c>
       <c r="AG153" t="s">
         <v>117</v>
       </c>
@@ -20098,7 +24884,31 @@
         <v>0.70705776084779703</v>
       </c>
     </row>
-    <row r="154" spans="33:41">
+    <row r="154" spans="2:41">
+      <c r="B154" t="s">
+        <v>244</v>
+      </c>
+      <c r="C154" t="s">
+        <v>128</v>
+      </c>
+      <c r="D154">
+        <v>5.3683930000000002</v>
+      </c>
+      <c r="K154" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="L154" t="s">
+        <v>270</v>
+      </c>
+      <c r="M154" t="s">
+        <v>274</v>
+      </c>
+      <c r="O154" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="P154" t="s">
+        <v>275</v>
+      </c>
       <c r="AG154" t="s">
         <v>118</v>
       </c>
@@ -20106,7 +24916,31 @@
         <v>0.49993067717510059</v>
       </c>
     </row>
-    <row r="155" spans="33:41">
+    <row r="155" spans="2:41">
+      <c r="B155" t="s">
+        <v>236</v>
+      </c>
+      <c r="C155" t="s">
+        <v>128</v>
+      </c>
+      <c r="D155">
+        <v>30.938687999999999</v>
+      </c>
+      <c r="K155" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="L155" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M155" s="27">
+        <v>13.27946</v>
+      </c>
+      <c r="O155" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="P155">
+        <v>19.818860933333333</v>
+      </c>
       <c r="AG155" t="s">
         <v>119</v>
       </c>
@@ -20114,7 +24948,31 @@
         <v>0.45825823360635898</v>
       </c>
     </row>
-    <row r="156" spans="33:41">
+    <row r="156" spans="2:41">
+      <c r="B156" t="s">
+        <v>237</v>
+      </c>
+      <c r="C156" t="s">
+        <v>128</v>
+      </c>
+      <c r="D156">
+        <v>31.456980000000001</v>
+      </c>
+      <c r="K156" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L156" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M156" s="27">
+        <v>18.098331000000002</v>
+      </c>
+      <c r="O156" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="P156">
+        <v>19.739341749999998</v>
+      </c>
       <c r="AG156" t="s">
         <v>120</v>
       </c>
@@ -20122,7 +24980,31 @@
         <v>3.8929200651529965</v>
       </c>
     </row>
-    <row r="157" spans="33:41" ht="15" thickBot="1">
+    <row r="157" spans="2:41" ht="15.75" thickBot="1">
+      <c r="B157" t="s">
+        <v>238</v>
+      </c>
+      <c r="C157" t="s">
+        <v>128</v>
+      </c>
+      <c r="D157">
+        <v>34.357607000000002</v>
+      </c>
+      <c r="K157" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L157" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M157" s="28">
+        <v>2.2134100000000001</v>
+      </c>
+      <c r="O157" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="P157">
+        <v>19.796141166666661</v>
+      </c>
       <c r="AG157" s="3" t="s">
         <v>101</v>
       </c>
@@ -20130,12 +25012,68 @@
         <v>14</v>
       </c>
     </row>
-    <row r="159" spans="33:41" ht="15" thickBot="1">
+    <row r="158" spans="2:41">
+      <c r="B158" t="s">
+        <v>239</v>
+      </c>
+      <c r="C158" t="s">
+        <v>128</v>
+      </c>
+      <c r="D158">
+        <v>39.090671999999998</v>
+      </c>
+      <c r="K158" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="L158" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M158" s="27">
+        <v>24.187462</v>
+      </c>
+    </row>
+    <row r="159" spans="2:41" ht="15.75" thickBot="1">
+      <c r="B159" t="s">
+        <v>241</v>
+      </c>
+      <c r="C159" t="s">
+        <v>128</v>
+      </c>
+      <c r="D159">
+        <v>38.751725</v>
+      </c>
+      <c r="K159" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="L159" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M159" s="27">
+        <v>13.098208</v>
+      </c>
       <c r="AG159" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="160" spans="33:41">
+    <row r="160" spans="2:41">
+      <c r="B160" t="s">
+        <v>243</v>
+      </c>
+      <c r="C160" t="s">
+        <v>128</v>
+      </c>
+      <c r="D160">
+        <v>25.324967000000001</v>
+      </c>
+      <c r="K160" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="L160" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M160" s="27">
+        <v>9.9307610000000004</v>
+      </c>
       <c r="AG160" s="4"/>
       <c r="AH160" s="4" t="s">
         <v>103</v>
@@ -20153,7 +25091,31 @@
         <v>129</v>
       </c>
     </row>
-    <row r="161" spans="33:41">
+    <row r="161" spans="2:41">
+      <c r="B161" t="s">
+        <v>244</v>
+      </c>
+      <c r="C161" t="s">
+        <v>128</v>
+      </c>
+      <c r="D161">
+        <v>24.631449</v>
+      </c>
+      <c r="K161" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="L161" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M161" s="27">
+        <v>18.789473999999998</v>
+      </c>
+      <c r="O161" t="s">
+        <v>109</v>
+      </c>
+      <c r="S161" t="s">
+        <v>174</v>
+      </c>
       <c r="AG161" t="s">
         <v>122</v>
       </c>
@@ -20173,7 +25135,31 @@
         <v>4.6857530529600564E-3</v>
       </c>
     </row>
-    <row r="162" spans="33:41">
+    <row r="162" spans="2:41" ht="15.75" thickBot="1">
+      <c r="B162" t="s">
+        <v>237</v>
+      </c>
+      <c r="C162" t="s">
+        <v>170</v>
+      </c>
+      <c r="D162">
+        <v>32.792991000000001</v>
+      </c>
+      <c r="K162" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="L162" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M162" s="27">
+        <v>13.606121</v>
+      </c>
+      <c r="T162" t="s">
+        <v>276</v>
+      </c>
+      <c r="U162" t="s">
+        <v>277</v>
+      </c>
       <c r="AG162" t="s">
         <v>123</v>
       </c>
@@ -20187,7 +25173,39 @@
         <v>15.15482663367081</v>
       </c>
     </row>
-    <row r="163" spans="33:41" ht="15" thickBot="1">
+    <row r="163" spans="2:41" ht="15.75" thickBot="1">
+      <c r="B163" t="s">
+        <v>240</v>
+      </c>
+      <c r="C163" t="s">
+        <v>170</v>
+      </c>
+      <c r="D163">
+        <v>17.652170000000002</v>
+      </c>
+      <c r="K163" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="L163" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M163" s="27">
+        <v>31.080375</v>
+      </c>
+      <c r="O163" s="33"/>
+      <c r="P163" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q163" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="S163" s="33"/>
+      <c r="T163" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="U163" s="33" t="s">
+        <v>98</v>
+      </c>
       <c r="AG163" s="3" t="s">
         <v>124</v>
       </c>
@@ -20201,8 +25219,81 @@
       <c r="AK163" s="3"/>
       <c r="AL163" s="3"/>
     </row>
-    <row r="164" spans="33:41" ht="15" thickBot="1"/>
-    <row r="165" spans="33:41">
+    <row r="164" spans="2:41" ht="15.75" thickBot="1">
+      <c r="B164" t="s">
+        <v>241</v>
+      </c>
+      <c r="C164" t="s">
+        <v>170</v>
+      </c>
+      <c r="D164">
+        <v>13.541086</v>
+      </c>
+      <c r="K164" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="L164" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M164" s="27">
+        <v>21.965651999999999</v>
+      </c>
+      <c r="O164" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="P164" s="31">
+        <v>19.818860933333333</v>
+      </c>
+      <c r="Q164" s="31">
+        <v>19.739341749999998</v>
+      </c>
+      <c r="S164" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="T164" s="31">
+        <v>19.818860933333333</v>
+      </c>
+      <c r="U164" s="31">
+        <v>19.739341749999998</v>
+      </c>
+    </row>
+    <row r="165" spans="2:41">
+      <c r="B165" t="s">
+        <v>242</v>
+      </c>
+      <c r="C165" t="s">
+        <v>170</v>
+      </c>
+      <c r="D165">
+        <v>22.615593000000001</v>
+      </c>
+      <c r="K165" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="L165" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M165" s="27">
+        <v>28.657671000000001</v>
+      </c>
+      <c r="O165" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="P165" s="31">
+        <v>125.39874790952246</v>
+      </c>
+      <c r="Q165" s="31">
+        <v>45.75766763921861</v>
+      </c>
+      <c r="S165" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="T165" s="31">
+        <v>125.39874790952246</v>
+      </c>
+      <c r="U165" s="31">
+        <v>45.75766763921861</v>
+      </c>
       <c r="AG165" s="4"/>
       <c r="AH165" s="4" t="s">
         <v>130</v>
@@ -20229,7 +25320,43 @@
         <v>135</v>
       </c>
     </row>
-    <row r="166" spans="33:41">
+    <row r="166" spans="2:41">
+      <c r="B166" t="s">
+        <v>243</v>
+      </c>
+      <c r="C166" t="s">
+        <v>170</v>
+      </c>
+      <c r="D166">
+        <v>60.294035000000001</v>
+      </c>
+      <c r="K166" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L166" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M166" s="27">
+        <v>29.803229999999999</v>
+      </c>
+      <c r="O166" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="P166" s="31">
+        <v>30</v>
+      </c>
+      <c r="Q166" s="31">
+        <v>12</v>
+      </c>
+      <c r="S166" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="T166" s="31">
+        <v>30</v>
+      </c>
+      <c r="U166" s="31">
+        <v>12</v>
+      </c>
       <c r="AG166" t="s">
         <v>125</v>
       </c>
@@ -20258,7 +25385,39 @@
         <v>15.654344838868695</v>
       </c>
     </row>
-    <row r="167" spans="33:41" ht="15" thickBot="1">
+    <row r="167" spans="2:41" ht="15.75" thickBot="1">
+      <c r="B167" t="s">
+        <v>245</v>
+      </c>
+      <c r="C167" t="s">
+        <v>170</v>
+      </c>
+      <c r="D167">
+        <v>27.407136999999999</v>
+      </c>
+      <c r="K167" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="L167" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M167" s="27">
+        <v>7.7812380000000001</v>
+      </c>
+      <c r="O167" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="P167" s="31">
+        <v>103.4974508351889</v>
+      </c>
+      <c r="Q167" s="31"/>
+      <c r="S167" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="T167" s="31">
+        <v>0</v>
+      </c>
+      <c r="U167" s="31"/>
       <c r="AG167" s="3" t="s">
         <v>136</v>
       </c>
@@ -20287,13 +25446,700 @@
         <v>0.55157109622808265</v>
       </c>
     </row>
+    <row r="168" spans="2:41">
+      <c r="B168" t="s">
+        <v>246</v>
+      </c>
+      <c r="C168" t="s">
+        <v>170</v>
+      </c>
+      <c r="D168">
+        <v>18.118190999999999</v>
+      </c>
+      <c r="K168" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="L168" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="M168" s="29">
+        <v>8.8605520000000002</v>
+      </c>
+      <c r="O168" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="P168" s="31">
+        <v>0</v>
+      </c>
+      <c r="Q168" s="31"/>
+      <c r="S168" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="T168" s="31">
+        <v>33</v>
+      </c>
+      <c r="U168" s="31"/>
+    </row>
+    <row r="169" spans="2:41">
+      <c r="B169" t="s">
+        <v>240</v>
+      </c>
+      <c r="C169" t="s">
+        <v>170</v>
+      </c>
+      <c r="D169">
+        <v>30.456852999999999</v>
+      </c>
+      <c r="K169" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="L169" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M169" s="27">
+        <v>10.206614999999999</v>
+      </c>
+      <c r="O169" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="P169" s="31">
+        <v>40</v>
+      </c>
+      <c r="Q169" s="31"/>
+      <c r="S169" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="T169" s="31">
+        <v>2.8126413882432311E-2</v>
+      </c>
+      <c r="U169" s="31"/>
+    </row>
+    <row r="170" spans="2:41">
+      <c r="B170" t="s">
+        <v>242</v>
+      </c>
+      <c r="C170" t="s">
+        <v>170</v>
+      </c>
+      <c r="D170">
+        <v>41.354227999999999</v>
+      </c>
+      <c r="F170" t="s">
+        <v>109</v>
+      </c>
+      <c r="K170" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="L170" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M170" s="27">
+        <v>26.940118999999999</v>
+      </c>
+      <c r="O170" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="P170" s="31">
+        <v>2.2884092248438195E-2</v>
+      </c>
+      <c r="Q170" s="31"/>
+      <c r="S170" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="T170" s="31">
+        <v>0.48886536899616073</v>
+      </c>
+      <c r="U170" s="31"/>
+    </row>
+    <row r="171" spans="2:41" ht="15.75" thickBot="1">
+      <c r="B171" t="s">
+        <v>245</v>
+      </c>
+      <c r="C171" t="s">
+        <v>170</v>
+      </c>
+      <c r="D171">
+        <v>20.296095999999999</v>
+      </c>
+      <c r="K171" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="L171" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M171" s="27">
+        <v>19.296327000000002</v>
+      </c>
+      <c r="O171" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="P171" s="31">
+        <v>0.4909282547457946</v>
+      </c>
+      <c r="Q171" s="31"/>
+      <c r="S171" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="T171" s="31">
+        <v>1.6923603090303456</v>
+      </c>
+      <c r="U171" s="31"/>
+    </row>
+    <row r="172" spans="2:41">
+      <c r="B172" t="s">
+        <v>246</v>
+      </c>
+      <c r="C172" t="s">
+        <v>170</v>
+      </c>
+      <c r="D172">
+        <v>35.347144999999998</v>
+      </c>
+      <c r="F172" s="33"/>
+      <c r="G172" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="H172" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="K172" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="L172" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M172" s="27">
+        <v>14.677982999999999</v>
+      </c>
+      <c r="O172" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="P172" s="31">
+        <v>1.6838510133356521</v>
+      </c>
+      <c r="Q172" s="31"/>
+      <c r="S172" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="T172" s="31">
+        <v>0.97773073799232146</v>
+      </c>
+      <c r="U172" s="31"/>
+    </row>
+    <row r="173" spans="2:41" ht="15.75" thickBot="1">
+      <c r="F173" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="G173" s="31">
+        <v>27.518001909090909</v>
+      </c>
+      <c r="H173" s="31">
+        <v>29.079593181818179</v>
+      </c>
+      <c r="K173" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="L173" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M173" s="27">
+        <v>20.567240000000002</v>
+      </c>
+      <c r="O173" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="P173" s="31">
+        <v>0.9818565094915892</v>
+      </c>
+      <c r="Q173" s="31"/>
+      <c r="S173" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="T173" s="32">
+        <v>2.0345152974493397</v>
+      </c>
+      <c r="U173" s="32"/>
+    </row>
+    <row r="174" spans="2:41" ht="15.75" thickBot="1">
+      <c r="F174" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="G174" s="31">
+        <v>160.12645664206229</v>
+      </c>
+      <c r="H174" s="31">
+        <v>179.38901862778238</v>
+      </c>
+      <c r="K174" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="L174" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M174" s="27">
+        <v>36.113652999999999</v>
+      </c>
+      <c r="O174" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="P174" s="32">
+        <v>2.0210753903062737</v>
+      </c>
+      <c r="Q174" s="32"/>
+    </row>
+    <row r="175" spans="2:41">
+      <c r="F175" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="G175" s="31">
+        <v>11</v>
+      </c>
+      <c r="H175" s="31">
+        <v>11</v>
+      </c>
+      <c r="K175" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L175" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M175" s="27">
+        <v>14.655714</v>
+      </c>
+    </row>
+    <row r="176" spans="2:41">
+      <c r="F176" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="G176" s="31">
+        <v>169.75773763492234</v>
+      </c>
+      <c r="H176" s="31"/>
+      <c r="K176" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L176" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M176" s="27">
+        <v>22.608398000000001</v>
+      </c>
+    </row>
+    <row r="177" spans="6:17">
+      <c r="F177" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="G177" s="31">
+        <v>0</v>
+      </c>
+      <c r="H177" s="31"/>
+      <c r="K177" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="L177" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M177" s="28">
+        <v>58.124909000000002</v>
+      </c>
+    </row>
+    <row r="178" spans="6:17">
+      <c r="F178" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G178" s="31">
+        <v>20</v>
+      </c>
+      <c r="H178" s="31"/>
+      <c r="K178" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="L178" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M178" s="27">
+        <v>23.981276999999999</v>
+      </c>
+      <c r="O178" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="179" spans="6:17" ht="15.75" thickBot="1">
+      <c r="F179" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="G179" s="31">
+        <v>-0.28108257830202393</v>
+      </c>
+      <c r="H179" s="31"/>
+      <c r="K179" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="L179" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M179" s="27">
+        <v>6.4825799999999996</v>
+      </c>
+    </row>
+    <row r="180" spans="6:17">
+      <c r="F180" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="G180" s="31">
+        <v>0.39076721757312882</v>
+      </c>
+      <c r="H180" s="31"/>
+      <c r="K180" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="L180" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M180" s="27">
+        <v>7.4210529999999997</v>
+      </c>
+      <c r="O180" s="33"/>
+      <c r="P180" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q180" s="33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="181" spans="6:17">
+      <c r="F181" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="G181" s="31">
+        <v>1.7247182429207868</v>
+      </c>
+      <c r="H181" s="31"/>
+      <c r="K181" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="L181" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M181" s="27">
+        <v>34.287424999999999</v>
+      </c>
+      <c r="O181" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="P181" s="31">
+        <v>19.818860933333333</v>
+      </c>
+      <c r="Q181" s="31">
+        <v>19.739341749999998</v>
+      </c>
+    </row>
+    <row r="182" spans="6:17">
+      <c r="F182" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="G182" s="31">
+        <v>0.78153443514625764</v>
+      </c>
+      <c r="H182" s="31"/>
+      <c r="K182" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="L182" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="M182" s="29">
+        <v>17.930986000000001</v>
+      </c>
+      <c r="O182" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="P182" s="31">
+        <v>125.39874790952246</v>
+      </c>
+      <c r="Q182" s="31">
+        <v>45.75766763921861</v>
+      </c>
+    </row>
+    <row r="183" spans="6:17" ht="15.75" thickBot="1">
+      <c r="F183" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="G183" s="32">
+        <v>2.0859634472658648</v>
+      </c>
+      <c r="H183" s="32"/>
+      <c r="K183" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="L183" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M183" s="30">
+        <v>21.611886999999999</v>
+      </c>
+      <c r="O183" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="P183" s="31">
+        <v>30</v>
+      </c>
+      <c r="Q183" s="31">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="184" spans="6:17">
+      <c r="K184" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="L184" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M184" s="30">
+        <v>18.307717</v>
+      </c>
+      <c r="O184" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="P184" s="31">
+        <v>29</v>
+      </c>
+      <c r="Q184" s="31">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185" spans="6:17">
+      <c r="K185" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="L185" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="M185" s="30">
+        <v>32.160544999999999</v>
+      </c>
+      <c r="O185" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="P185" s="31">
+        <v>2.740496934814133</v>
+      </c>
+      <c r="Q185" s="31"/>
+    </row>
+    <row r="186" spans="6:17">
+      <c r="F186" t="s">
+        <v>160</v>
+      </c>
+      <c r="K186" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="L186" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="M186" s="30">
+        <v>15.797788000000001</v>
+      </c>
+      <c r="O186" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="P186" s="31">
+        <v>4.0303913311506595E-2</v>
+      </c>
+      <c r="Q186" s="31"/>
+    </row>
+    <row r="187" spans="6:17" ht="15.75" thickBot="1">
+      <c r="K187" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="L187" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="M187" s="30">
+        <v>18.728362000000001</v>
+      </c>
+      <c r="O187" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="P187" s="32">
+        <v>2.5758605989686227</v>
+      </c>
+      <c r="Q187" s="32"/>
+    </row>
+    <row r="188" spans="6:17">
+      <c r="F188" s="33"/>
+      <c r="G188" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="H188" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="K188" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="L188" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="M188" s="30">
+        <v>26.720863999999999</v>
+      </c>
+    </row>
+    <row r="189" spans="6:17">
+      <c r="F189" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="G189" s="31">
+        <v>27.518001909090909</v>
+      </c>
+      <c r="H189" s="31">
+        <v>29.079593181818179</v>
+      </c>
+      <c r="K189" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L189" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="M189" s="30">
+        <v>11.462300000000001</v>
+      </c>
+    </row>
+    <row r="190" spans="6:17">
+      <c r="F190" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="G190" s="31">
+        <v>160.12645664206229</v>
+      </c>
+      <c r="H190" s="31">
+        <v>179.38901862778238</v>
+      </c>
+      <c r="K190" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="L190" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="M190" s="30">
+        <v>14.210526</v>
+      </c>
+    </row>
+    <row r="191" spans="6:17">
+      <c r="F191" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="G191" s="31">
+        <v>11</v>
+      </c>
+      <c r="H191" s="31">
+        <v>11</v>
+      </c>
+      <c r="K191" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="L191" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="M191" s="30">
+        <v>10.094481</v>
+      </c>
+    </row>
+    <row r="192" spans="6:17">
+      <c r="F192" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G192" s="31">
+        <v>10</v>
+      </c>
+      <c r="H192" s="31">
+        <v>10</v>
+      </c>
+      <c r="K192" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="L192" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="M192" s="30">
+        <v>20.227074999999999</v>
+      </c>
+    </row>
+    <row r="193" spans="6:13">
+      <c r="F193" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="G193" s="31">
+        <v>0.8926212867818385</v>
+      </c>
+      <c r="H193" s="31"/>
+      <c r="K193" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="L193" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="M193" s="30">
+        <v>28.883882</v>
+      </c>
+    </row>
+    <row r="194" spans="6:13">
+      <c r="F194" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="G194" s="31">
+        <v>0.43048756108334429</v>
+      </c>
+      <c r="H194" s="31"/>
+      <c r="K194" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="L194" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="M194" s="30">
+        <v>21.452435999999999</v>
+      </c>
+    </row>
+    <row r="195" spans="6:13" ht="15.75" thickBot="1">
+      <c r="F195" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="G195" s="32">
+        <v>0.33576911259918313</v>
+      </c>
+      <c r="H195" s="32"/>
+      <c r="K195" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="L195" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="M195" s="30">
+        <v>17.541353000000001</v>
+      </c>
+    </row>
+    <row r="196" spans="6:13">
+      <c r="K196" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="L196" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="M196" s="30">
+        <v>19.592489</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <tableParts count="2">
-    <tablePart r:id="rId3"/>
-    <tablePart r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <drawing r:id="rId4"/>
+  <tableParts count="6">
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
 </file>
@@ -20301,18 +26147,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02490D31-8144-4D02-A37F-D0BDE3454DA1}">
   <dimension ref="D2:Y34"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="9" max="9" width="11.81640625" customWidth="1"/>
-    <col min="10" max="10" width="10.453125" customWidth="1"/>
-    <col min="11" max="11" width="12.81640625" customWidth="1"/>
-    <col min="12" max="12" width="16.54296875" customWidth="1"/>
-    <col min="13" max="13" width="18.1796875" customWidth="1"/>
-    <col min="16" max="16" width="11.81640625" customWidth="1"/>
-    <col min="17" max="17" width="10.453125" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" customWidth="1"/>
+    <col min="12" max="12" width="16.5703125" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" customWidth="1"/>
+    <col min="16" max="16" width="11.85546875" customWidth="1"/>
+    <col min="17" max="17" width="10.42578125" customWidth="1"/>
     <col min="18" max="18" width="12" customWidth="1"/>
-    <col min="19" max="19" width="11.54296875" customWidth="1"/>
-    <col min="20" max="20" width="11.81640625" customWidth="1"/>
+    <col min="19" max="19" width="11.5703125" customWidth="1"/>
+    <col min="20" max="20" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="4:20">
@@ -20825,7 +26671,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="19" spans="4:25" ht="15" thickBot="1">
+    <row r="19" spans="4:25" ht="15.75" thickBot="1">
       <c r="H19" s="2"/>
       <c r="O19" t="s">
         <v>179</v>
@@ -20965,7 +26811,7 @@
         <v>1.3334667165923608</v>
       </c>
     </row>
-    <row r="27" spans="4:25" ht="15" thickBot="1">
+    <row r="27" spans="4:25" ht="15.75" thickBot="1">
       <c r="H27" s="2"/>
       <c r="J27" s="3" t="s">
         <v>162</v>
@@ -20997,7 +26843,7 @@
         <v>0.20366980711260271</v>
       </c>
     </row>
-    <row r="30" spans="4:25" ht="15" thickBot="1">
+    <row r="30" spans="4:25" ht="15.75" thickBot="1">
       <c r="R30" s="3" t="s">
         <v>108</v>
       </c>
@@ -21025,15 +26871,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFC0AEBE-0304-40C9-AD55-B102AE5944DF}">
   <dimension ref="B1:T49"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="7" max="7" width="12.453125" customWidth="1"/>
-    <col min="8" max="9" width="10.81640625" customWidth="1"/>
-    <col min="10" max="10" width="11.453125" customWidth="1"/>
-    <col min="14" max="14" width="9.453125" customWidth="1"/>
-    <col min="15" max="15" width="10.81640625" customWidth="1"/>
-    <col min="16" max="16" width="9.81640625" customWidth="1"/>
-    <col min="17" max="17" width="19.453125" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="9" width="10.85546875" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" customWidth="1"/>
+    <col min="16" max="16" width="9.85546875" customWidth="1"/>
+    <col min="17" max="17" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:20">
@@ -21510,7 +27356,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="6:16" ht="15" thickBot="1">
+    <row r="20" spans="6:16" ht="15.75" thickBot="1">
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="6:16">
@@ -21641,7 +27487,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="6:16" ht="15" thickBot="1">
+    <row r="28" spans="6:16" ht="15.75" thickBot="1">
       <c r="F28" s="10"/>
       <c r="I28" s="3" t="s">
         <v>162</v>
@@ -21682,7 +27528,7 @@
         <v>1.6643182532567993E-2</v>
       </c>
     </row>
-    <row r="32" spans="6:16" ht="15" thickBot="1">
+    <row r="32" spans="6:16" ht="15.75" thickBot="1">
       <c r="N32" s="3" t="s">
         <v>108</v>
       </c>
@@ -21696,7 +27542,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="37" spans="2:4" ht="15" thickBot="1"/>
+    <row r="37" spans="2:4" ht="15.75" thickBot="1"/>
     <row r="38" spans="2:4">
       <c r="B38" s="4"/>
       <c r="C38" s="4" t="s">
@@ -21795,7 +27641,7 @@
         <v>4.3206917156444202E-2</v>
       </c>
     </row>
-    <row r="49" spans="2:4" ht="15" thickBot="1">
+    <row r="49" spans="2:4" ht="15.75" thickBot="1">
       <c r="B49" s="3" t="s">
         <v>108</v>
       </c>
@@ -21818,13 +27664,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D375B1A-F51E-4B8D-9DD1-817BE0164FEC}">
   <dimension ref="B1:AE31"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.7265625" customWidth="1"/>
-    <col min="8" max="8" width="18.81640625" customWidth="1"/>
-    <col min="9" max="9" width="15.7265625" customWidth="1"/>
-    <col min="10" max="10" width="16.7265625" customWidth="1"/>
-    <col min="19" max="19" width="8.7265625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
+    <col min="19" max="19" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:31">
@@ -22950,7 +28796,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="3:10" ht="15" thickBot="1">
+    <row r="19" spans="3:10" ht="15.75" thickBot="1">
       <c r="D19" t="s">
         <v>196</v>
       </c>
@@ -23085,7 +28931,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="3:10" ht="15" thickBot="1">
+    <row r="27" spans="3:10" ht="15.75" thickBot="1">
       <c r="C27" s="3" t="s">
         <v>162</v>
       </c>
@@ -23124,7 +28970,7 @@
         <v>0.101265379818601</v>
       </c>
     </row>
-    <row r="31" spans="3:10" ht="15" thickBot="1">
+    <row r="31" spans="3:10" ht="15.75" thickBot="1">
       <c r="H31" s="3" t="s">
         <v>108</v>
       </c>
@@ -23145,17 +28991,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2EABC84-23BA-464A-9765-728455CFA12E}">
   <dimension ref="B3:G17"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.6328125" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="23.6328125" customWidth="1"/>
-    <col min="5" max="5" width="24.36328125" customWidth="1"/>
-    <col min="6" max="6" width="23.08984375" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="24.42578125" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" customWidth="1"/>
     <col min="7" max="7" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" ht="29">
+    <row r="3" spans="2:7" ht="30">
       <c r="B3" s="15" t="s">
         <v>212</v>
       </c>
@@ -23175,7 +29021,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="43.5">
+    <row r="4" spans="2:7" ht="45">
       <c r="B4" s="16" t="s">
         <v>213</v>
       </c>
@@ -23213,7 +29059,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="58">
+    <row r="6" spans="2:7" ht="60">
       <c r="B6" s="16" t="s">
         <v>210</v>
       </c>
@@ -23233,7 +29079,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="29">
+    <row r="7" spans="2:7" ht="30">
       <c r="B7" s="16" t="s">
         <v>219</v>
       </c>
